--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E762BF-3975-4444-B856-F95209A0CB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A4A9EB-5533-4F5F-A30D-85AAC18B4670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5971,7 +5971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66271703-46B6-43FA-82A9-10B7B8752D59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002B96B9-060F-49B3-AD90-085A6BC96817}">
   <dimension ref="B2:AG1095"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30930,7 +30930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E53B7-0808-4471-9F7A-9E12075C79E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF41F09-C9AC-4706-920B-92757D638F74}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43330,7 +43330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDEA11D-0899-492E-AE3D-203776A208FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96685F87-6D64-439D-872B-1AE9C03997AA}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A4A9EB-5533-4F5F-A30D-85AAC18B4670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A720F7-AACF-49AA-B082-AEB9680EA02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5971,7 +5971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002B96B9-060F-49B3-AD90-085A6BC96817}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA53499D-166B-419B-AE0E-4408D09013BB}">
   <dimension ref="B2:AG1095"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6047,7 +6047,7 @@
         <v>113</v>
       </c>
       <c r="C4">
-        <v>1.1060010431731064</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D4">
         <v>408.1</v>
@@ -6118,7 +6118,7 @@
         <v>114</v>
       </c>
       <c r="C5">
-        <v>2.2120020863462129</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D5">
         <v>99.000000000000014</v>
@@ -6186,7 +6186,7 @@
         <v>115</v>
       </c>
       <c r="C6">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D6">
         <v>261.8</v>
@@ -6251,7 +6251,7 @@
         <v>116</v>
       </c>
       <c r="C7">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -6301,7 +6301,7 @@
         <v>117</v>
       </c>
       <c r="C8">
-        <v>6.4349151602798935</v>
+        <v>4.5044406121959248</v>
       </c>
       <c r="D8">
         <v>313.5</v>
@@ -6351,7 +6351,7 @@
         <v>118</v>
       </c>
       <c r="C9">
-        <v>5.451803121903799</v>
+        <v>3.816262185332659</v>
       </c>
       <c r="D9">
         <v>159.5</v>
@@ -6401,7 +6401,7 @@
         <v>119</v>
       </c>
       <c r="C10">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D10">
         <v>245.3</v>
@@ -6451,7 +6451,7 @@
         <v>120</v>
       </c>
       <c r="C11">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D11">
         <v>590.70000000000005</v>
@@ -6501,7 +6501,7 @@
         <v>121</v>
       </c>
       <c r="C12">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D12">
         <v>400.40000000000003</v>
@@ -6551,7 +6551,7 @@
         <v>122</v>
       </c>
       <c r="C13">
-        <v>1.8433350719551778</v>
+        <v>1.2903345503686243</v>
       </c>
       <c r="D13">
         <v>112.2</v>
@@ -6601,7 +6601,7 @@
         <v>123</v>
       </c>
       <c r="C14">
-        <v>0.92166753597758888</v>
+        <v>0.64516727518431216</v>
       </c>
       <c r="D14">
         <v>124.30000000000001</v>
@@ -6651,7 +6651,7 @@
         <v>124</v>
       </c>
       <c r="C15">
-        <v>2.7650026079327663</v>
+        <v>1.9355018255529364</v>
       </c>
       <c r="D15">
         <v>167.20000000000002</v>
@@ -6701,7 +6701,7 @@
         <v>125</v>
       </c>
       <c r="C16">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D16">
         <v>401.50000000000006</v>
@@ -6751,7 +6751,7 @@
         <v>126</v>
       </c>
       <c r="C17">
-        <v>4.6083376798879421</v>
+        <v>3.2258363759215594</v>
       </c>
       <c r="D17">
         <v>132</v>
@@ -6801,7 +6801,7 @@
         <v>127</v>
       </c>
       <c r="C18">
-        <v>2.7650026079327663</v>
+        <v>1.9355018255529364</v>
       </c>
       <c r="D18">
         <v>165</v>
@@ -6851,7 +6851,7 @@
         <v>128</v>
       </c>
       <c r="C19">
-        <v>1.8433350719551769</v>
+        <v>1.2903345503686237</v>
       </c>
       <c r="D19">
         <v>39.6</v>
@@ -6901,7 +6901,7 @@
         <v>129</v>
       </c>
       <c r="C20">
-        <v>0.92166753597758888</v>
+        <v>0.64516727518431216</v>
       </c>
       <c r="D20">
         <v>244.20000000000002</v>
@@ -6951,7 +6951,7 @@
         <v>130</v>
       </c>
       <c r="C21">
-        <v>1.8433350719551769</v>
+        <v>1.2903345503686237</v>
       </c>
       <c r="D21">
         <v>397.1</v>
@@ -7001,7 +7001,7 @@
         <v>131</v>
       </c>
       <c r="C22">
-        <v>4.4240041726924257</v>
+        <v>3.0968029208846977</v>
       </c>
       <c r="D22">
         <v>275</v>
@@ -7051,7 +7051,7 @@
         <v>132</v>
       </c>
       <c r="C23">
-        <v>2.2120020863462129</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D23">
         <v>323.40000000000003</v>
@@ -7101,7 +7101,7 @@
         <v>133</v>
       </c>
       <c r="C24">
-        <v>4.4686910835277036</v>
+        <v>3.1280837584693924</v>
       </c>
       <c r="D24">
         <v>280.5</v>
@@ -7151,7 +7151,7 @@
         <v>134</v>
       </c>
       <c r="C25">
-        <v>1.8433350719551778</v>
+        <v>1.2903345503686243</v>
       </c>
       <c r="D25">
         <v>273.90000000000003</v>
@@ -7201,7 +7201,7 @@
         <v>135</v>
       </c>
       <c r="C26">
-        <v>1.1060010431731064</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D26">
         <v>221.10000000000002</v>
@@ -7251,7 +7251,7 @@
         <v>136</v>
       </c>
       <c r="C27">
-        <v>3.6866701439103546</v>
+        <v>2.5806691007372482</v>
       </c>
       <c r="D27">
         <v>103.4</v>
@@ -7301,7 +7301,7 @@
         <v>137</v>
       </c>
       <c r="C28">
-        <v>2.7650026079327663</v>
+        <v>1.9355018255529364</v>
       </c>
       <c r="D28">
         <v>110.00000000000001</v>
@@ -7351,7 +7351,7 @@
         <v>138</v>
       </c>
       <c r="C29">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D29">
         <v>279.40000000000003</v>
@@ -7401,7 +7401,7 @@
         <v>139</v>
       </c>
       <c r="C30">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D30">
         <v>437.8</v>
@@ -7451,7 +7451,7 @@
         <v>140</v>
       </c>
       <c r="C31">
-        <v>6.6806931698739174</v>
+        <v>4.6764852189117416</v>
       </c>
       <c r="D31">
         <v>305.8</v>
@@ -7501,7 +7501,7 @@
         <v>141</v>
       </c>
       <c r="C32">
-        <v>4.6697821822864496</v>
+        <v>3.2688475276005144</v>
       </c>
       <c r="D32">
         <v>537.90000000000009</v>
@@ -7551,7 +7551,7 @@
         <v>142</v>
       </c>
       <c r="C33">
-        <v>0.92166753597758888</v>
+        <v>0.64516727518431216</v>
       </c>
       <c r="D33">
         <v>245.3</v>
@@ -7601,7 +7601,7 @@
         <v>143</v>
       </c>
       <c r="C34">
-        <v>3.6866701439103546</v>
+        <v>2.5806691007372482</v>
       </c>
       <c r="D34">
         <v>74.800000000000011</v>
@@ -7651,7 +7651,7 @@
         <v>144</v>
       </c>
       <c r="C35">
-        <v>1.474668057564142</v>
+        <v>1.0322676402948994</v>
       </c>
       <c r="D35">
         <v>95.7</v>
@@ -7701,7 +7701,7 @@
         <v>145</v>
       </c>
       <c r="C36">
-        <v>1.8433350719551769</v>
+        <v>1.2903345503686237</v>
       </c>
       <c r="D36">
         <v>463.1</v>
@@ -7751,7 +7751,7 @@
         <v>146</v>
       </c>
       <c r="C37">
-        <v>4.4240041726924257</v>
+        <v>3.0968029208846977</v>
       </c>
       <c r="D37">
         <v>119.9</v>
@@ -7801,7 +7801,7 @@
         <v>147</v>
       </c>
       <c r="C38">
-        <v>2.2120020863462129</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D38">
         <v>647.90000000000009</v>
@@ -7851,7 +7851,7 @@
         <v>148</v>
       </c>
       <c r="C39">
-        <v>3.6866701439103546</v>
+        <v>2.5806691007372482</v>
       </c>
       <c r="D39">
         <v>205.70000000000002</v>
@@ -7901,7 +7901,7 @@
         <v>149</v>
       </c>
       <c r="C40">
-        <v>7.418027198655988</v>
+        <v>5.1926190390591911</v>
       </c>
       <c r="D40">
         <v>250.8</v>
@@ -7951,7 +7951,7 @@
         <v>150</v>
       </c>
       <c r="C41">
-        <v>6.9264711794679403</v>
+        <v>4.8485298256275575</v>
       </c>
       <c r="D41">
         <v>51.7</v>
@@ -8001,7 +8001,7 @@
         <v>151</v>
       </c>
       <c r="C42">
-        <v>4.4686910835277036</v>
+        <v>3.1280837584693924</v>
       </c>
       <c r="D42">
         <v>218.9</v>
@@ -8051,7 +8051,7 @@
         <v>152</v>
       </c>
       <c r="C43">
-        <v>3.6866701439103537</v>
+        <v>2.5806691007372473</v>
       </c>
       <c r="D43">
         <v>78.100000000000009</v>
@@ -8101,7 +8101,7 @@
         <v>153</v>
       </c>
       <c r="C44">
-        <v>11.104697342566341</v>
+        <v>7.7732881397964384</v>
       </c>
       <c r="D44">
         <v>447.70000000000005</v>
@@ -8151,7 +8151,7 @@
         <v>154</v>
       </c>
       <c r="C45">
-        <v>8.2950078237982954</v>
+        <v>5.8065054766588062</v>
       </c>
       <c r="D45">
         <v>138.60000000000002</v>
@@ -8201,7 +8201,7 @@
         <v>155</v>
       </c>
       <c r="C46">
-        <v>2.2120020863462129</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D46">
         <v>119.9</v>
@@ -8251,7 +8251,7 @@
         <v>156</v>
       </c>
       <c r="C47">
-        <v>1.8433350719551769</v>
+        <v>1.2903345503686237</v>
       </c>
       <c r="D47">
         <v>45.1</v>
@@ -8301,7 +8301,7 @@
         <v>157</v>
       </c>
       <c r="C48">
-        <v>0.49155601918804742</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D48">
         <v>93.500000000000014</v>
@@ -8351,7 +8351,7 @@
         <v>158</v>
       </c>
       <c r="C49">
-        <v>4.4240041726924257</v>
+        <v>3.0968029208846977</v>
       </c>
       <c r="D49">
         <v>370.70000000000005</v>
@@ -8401,7 +8401,7 @@
         <v>159</v>
       </c>
       <c r="C50">
-        <v>2.2120020863462129</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D50">
         <v>192.50000000000003</v>
@@ -8451,7 +8451,7 @@
         <v>160</v>
       </c>
       <c r="C51">
-        <v>1.1060010431731064</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D51">
         <v>112.2</v>
@@ -8501,7 +8501,7 @@
         <v>161</v>
       </c>
       <c r="C52">
-        <v>1.1060010431731064</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D52">
         <v>151.80000000000001</v>
@@ -8551,7 +8551,7 @@
         <v>162</v>
       </c>
       <c r="C53">
-        <v>1.1060010431731064</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D53">
         <v>125.4</v>
@@ -30930,7 +30930,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF41F09-C9AC-4706-920B-92757D638F74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A71DE700-A27E-4C91-A5A9-1E20D04241E3}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43330,7 +43330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96685F87-6D64-439D-872B-1AE9C03997AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E116D57B-EC40-45D0-B343-720485510AB6}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FAABA6-5F81-41B9-B186-33067A7F6511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B21308-F981-478B-82BC-C550A782E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6199,7 +6199,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DEC2A08-80A1-4F7B-99F2-A15064F588DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C5BC12-3DBB-4DED-9477-A231BD0D1A3C}">
   <dimension ref="B2:AG1173"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32706,7 +32706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38405006-6461-45A4-BC30-20B02F3B4ADB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A616D6EF-0B84-416A-9086-06539061F13C}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45106,7 +45106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCA4C3D4-636F-4BAB-855E-8FAEF9015849}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8170FF64-1F2D-40AD-9DD7-3969E72D7346}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBE7CD7-BB38-49AC-BA8C-7640CC3A7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B02C5E6-F19B-4796-B19D-83D6D6F286B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10108" uniqueCount="1778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10112" uniqueCount="1781">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -5412,6 +5412,15 @@
   </si>
   <si>
     <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>*ccs-rf</t>
   </si>
 </sst>
 </file>
@@ -5886,7 +5895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E1EC7-2E61-4DC3-B37B-7E050A1433CE}">
-  <dimension ref="B2:I11"/>
+  <dimension ref="A2:I12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -5898,12 +5907,15 @@
     <col min="9" max="9" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>1276</v>
+      </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -5923,7 +5935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -5941,7 +5953,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -5959,7 +5971,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -5977,7 +5989,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -5991,7 +6003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -6005,7 +6017,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -6020,7 +6032,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>50</v>
       </c>
@@ -6031,7 +6043,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>51</v>
       </c>
@@ -6040,6 +6052,20 @@
       </c>
       <c r="G11" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E12">
+        <v>2100</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1780</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B02C5E6-F19B-4796-B19D-83D6D6F286B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479FB9C6-3020-48F1-9F4F-807A903EB1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10112" uniqueCount="1781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10108" uniqueCount="1778">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -5412,15 +5412,6 @@
   </si>
   <si>
     <t>elc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>CHP</t>
-  </si>
-  <si>
-    <t>*ccs-rf</t>
   </si>
 </sst>
 </file>
@@ -5895,7 +5886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E1EC7-2E61-4DC3-B37B-7E050A1433CE}">
-  <dimension ref="A2:I12"/>
+  <dimension ref="B2:I11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -5907,15 +5898,12 @@
     <col min="9" max="9" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>1276</v>
-      </c>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -5935,7 +5923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -5953,7 +5941,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -5971,7 +5959,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -5989,7 +5977,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -6003,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -6017,7 +6005,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -6032,7 +6020,7 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>50</v>
       </c>
@@ -6043,7 +6031,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>51</v>
       </c>
@@ -6052,20 +6040,6 @@
       </c>
       <c r="G11" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>1779</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1778</v>
-      </c>
-      <c r="E12">
-        <v>2100</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1780</v>
       </c>
     </row>
   </sheetData>
@@ -6075,7 +6049,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9CCD66-2533-470C-A27C-D704E5585716}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB35593-B4ED-491F-9EE1-8EDE4FCC2056}">
   <dimension ref="B2:AG1147"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31378,7 +31352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DFC528-17C7-4274-8AE5-7644EE9AF0A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E88F6D-9A05-4A61-8A8A-DB37DDE35CE6}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43780,7 +43754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C2A1A1-8C3A-4CC9-BD50-BA103A44D8AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB7D14C-3FB3-4277-90D6-ED7E5D182A59}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479FB9C6-3020-48F1-9F4F-807A903EB1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC89F05-A5A5-455B-A6A6-BA90C93470A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6049,7 +6049,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB35593-B4ED-491F-9EE1-8EDE4FCC2056}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C02B2FDB-269B-4CC5-810B-BD103C80B9B9}">
   <dimension ref="B2:AG1147"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31352,7 +31352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46E88F6D-9A05-4A61-8A8A-DB37DDE35CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EA42FAC-A3C6-4793-8CA8-54EB554FFDE7}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43754,7 +43754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FB7D14C-3FB3-4277-90D6-ED7E5D182A59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C8B2FDA-2C7D-4A6E-8291-B4ACB355EA89}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FF7E0D-E5F6-48C5-98AE-C50AD8E94AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5341B38D-0660-47D1-81B9-963770089DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10410" uniqueCount="1830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10413" uniqueCount="1832">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -5568,6 +5568,12 @@
   </si>
   <si>
     <t>elc_won_AUS_097</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>bio*</t>
   </si>
 </sst>
 </file>
@@ -6042,7 +6048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E1EC7-2E61-4DC3-B37B-7E050A1433CE}">
-  <dimension ref="B2:I11"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -6050,16 +6056,17 @@
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -6076,10 +6083,13 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -6090,14 +6100,14 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <f>I4*3.6</f>
+        <f>J4*3.6</f>
         <v>338.40000000000003</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -6108,14 +6118,14 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <f>I5*3.6</f>
+        <f>J5*3.6</f>
         <v>198</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -6126,14 +6136,14 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <f>I6*3.6</f>
+        <f>J6*3.6</f>
         <v>252</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -6147,7 +6157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -6161,7 +6171,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -6176,26 +6186,37 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="E10">
         <v>50</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>51</v>
       </c>
       <c r="E11">
         <v>8.76</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E12">
+        <v>2100</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1831</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5341B38D-0660-47D1-81B9-963770089DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA708CB-5F94-4103-B14E-2BE39A355342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="emissions" sheetId="5" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10413" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10410" uniqueCount="1830">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -419,12 +419,12 @@
     <t>efficiency</t>
   </si>
   <si>
-    <t>g_Armidale_AUS-Brisbane_AUS</t>
-  </si>
-  <si>
     <t>g_Armidale_AUS-BulliCreek_AUS</t>
   </si>
   <si>
+    <t>g_Armidale_AUS-Ipswich_AUS</t>
+  </si>
+  <si>
     <t>g_Australind_AUS-Merredin_AUS</t>
   </si>
   <si>
@@ -494,9 +494,6 @@
     <t>g_GinGin_AUS-Tarong_AUS</t>
   </si>
   <si>
-    <t>g_Hobart_AUS-Palmerston_AUS</t>
-  </si>
-  <si>
     <t>g_Karratha_AUS-TomPriceMine_AUS</t>
   </si>
   <si>
@@ -521,6 +518,9 @@
     <t>g_OlympicDamWest_AUS-Davenport_AUS</t>
   </si>
   <si>
+    <t>g_Palmerston_AUS-Kingston_AUS</t>
+  </si>
+  <si>
     <t>g_Palmerston_AUS-Sheffield_AUS</t>
   </si>
   <si>
@@ -554,12 +554,12 @@
     <t>g_SydneyWest_AUS-CentralCoast_AUS</t>
   </si>
   <si>
-    <t>g_Tarong_AUS-Brisbane_AUS</t>
-  </si>
-  <si>
     <t>g_Tarong_AUS-BulliCreek_AUS</t>
   </si>
   <si>
+    <t>g_Tarong_AUS-Ipswich_AUS</t>
+  </si>
+  <si>
     <t>g_Tarong_AUS-WandoanSouth_AUS</t>
   </si>
   <si>
@@ -638,6 +638,9 @@
     <t>e_demand_Tarong_AUS</t>
   </si>
   <si>
+    <t>e_demand_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>e_demand_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -650,9 +653,6 @@
     <t>e_demand_Para_AUS</t>
   </si>
   <si>
-    <t>e_demand_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>e_demand_BulliCreek_AUS</t>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <t>e_demand_Horsham_AUS</t>
   </si>
   <si>
-    <t>e_demand_Hobart_AUS</t>
+    <t>e_demand_Kingston_AUS</t>
   </si>
   <si>
     <t>e_demand_Kalgoorlie_AUS</t>
@@ -734,6 +734,9 @@
     <t>ev_battery_Tarong_AUS</t>
   </si>
   <si>
+    <t>ev_battery_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>ev_battery_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -746,9 +749,6 @@
     <t>ev_battery_Para_AUS</t>
   </si>
   <si>
-    <t>ev_battery_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>ev_battery_BulliCreek_AUS</t>
   </si>
   <si>
@@ -788,7 +788,7 @@
     <t>ev_battery_Horsham_AUS</t>
   </si>
   <si>
-    <t>ev_battery_Hobart_AUS</t>
+    <t>ev_battery_Kingston_AUS</t>
   </si>
   <si>
     <t>ev_battery_Kalgoorlie_AUS</t>
@@ -830,6 +830,9 @@
     <t>H2prd_Elc_PEM_Tarong_AUS</t>
   </si>
   <si>
+    <t>H2prd_Elc_PEM_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>H2prd_Elc_PEM_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -842,9 +845,6 @@
     <t>H2prd_Elc_PEM_Para_AUS</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>H2prd_Elc_PEM_BulliCreek_AUS</t>
   </si>
   <si>
@@ -884,7 +884,7 @@
     <t>H2prd_Elc_PEM_Horsham_AUS</t>
   </si>
   <si>
-    <t>H2prd_Elc_PEM_Hobart_AUS</t>
+    <t>H2prd_Elc_PEM_Kingston_AUS</t>
   </si>
   <si>
     <t>H2prd_Elc_PEM_Kalgoorlie_AUS</t>
@@ -926,6 +926,9 @@
     <t>H2prd_Elc_ALK_Tarong_AUS</t>
   </si>
   <si>
+    <t>H2prd_Elc_ALK_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>H2prd_Elc_ALK_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -938,9 +941,6 @@
     <t>H2prd_Elc_ALK_Para_AUS</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>H2prd_Elc_ALK_BulliCreek_AUS</t>
   </si>
   <si>
@@ -980,7 +980,7 @@
     <t>H2prd_Elc_ALK_Horsham_AUS</t>
   </si>
   <si>
-    <t>H2prd_Elc_ALK_Hobart_AUS</t>
+    <t>H2prd_Elc_ALK_Kingston_AUS</t>
   </si>
   <si>
     <t>H2prd_Elc_ALK_Kalgoorlie_AUS</t>
@@ -1094,7 +1094,7 @@
     <t>het_industry</t>
   </si>
   <si>
-    <t>h_demand_Brisbane_AUS</t>
+    <t>h_demand_Ipswich_AUS</t>
   </si>
   <si>
     <t>h_demand_Strathmore_AUS</t>
@@ -1175,6 +1175,9 @@
     <t>e_Tarong_AUS</t>
   </si>
   <si>
+    <t>e_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>e_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -1187,9 +1190,6 @@
     <t>e_Para_AUS</t>
   </si>
   <si>
-    <t>e_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>e_BulliCreek_AUS</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>e_Horsham_AUS</t>
   </si>
   <si>
-    <t>e_Hobart_AUS</t>
+    <t>e_Kingston_AUS</t>
   </si>
   <si>
     <t>e_Kalgoorlie_AUS</t>
@@ -1262,7 +1262,7 @@
     <t>h_Perth_AUS</t>
   </si>
   <si>
-    <t>h_Brisbane_AUS</t>
+    <t>h_Ipswich_AUS</t>
   </si>
   <si>
     <t>h_Strathmore_AUS</t>
@@ -2108,6 +2108,57 @@
     <t>en_hp_air_10mw_Tarong_AUS</t>
   </si>
   <si>
+    <t>en_gas_ccgt_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_nuclear_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_biomass_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>en_gas_ccgt_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -2369,57 +2420,6 @@
     <t>en_hp_air_10mw_Para_AUS</t>
   </si>
   <si>
-    <t>en_gas_ccgt_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_nuclear_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_biomass_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_BulliCreek_AUS</t>
   </si>
   <si>
@@ -3605,6 +3605,60 @@
     <t>en_hp_air_10mw_Horsham_AUS</t>
   </si>
   <si>
+    <t>en_gas_ccgt_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_nuclear_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_biomass_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>h_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Kingston_AUS</t>
+  </si>
+  <si>
     <t>en_gas_ccgt_PortHedland_AUS</t>
   </si>
   <si>
@@ -3659,60 +3713,6 @@
     <t>en_hp_air_10mw_PortHedland_AUS</t>
   </si>
   <si>
-    <t>en_gas_ccgt_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_nuclear_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_biomass_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>h_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_Hobart_AUS</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Kalgoorlie_AUS</t>
   </si>
   <si>
@@ -3857,6 +3857,12 @@
     <t>en_battery_8h_Tarong_AUS</t>
   </si>
   <si>
+    <t>en_battery_4h_Ipswich_AUS</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Ipswich_AUS</t>
+  </si>
+  <si>
     <t>en_battery_4h_Bouldercombe_AUS</t>
   </si>
   <si>
@@ -3887,12 +3893,6 @@
     <t>en_battery_8h_Para_AUS</t>
   </si>
   <si>
-    <t>en_battery_4h_Brisbane_AUS</t>
-  </si>
-  <si>
-    <t>en_battery_8h_Brisbane_AUS</t>
-  </si>
-  <si>
     <t>en_battery_4h_BulliCreek_AUS</t>
   </si>
   <si>
@@ -4025,18 +4025,18 @@
     <t>en_battery_8h_Horsham_AUS</t>
   </si>
   <si>
+    <t>en_battery_4h_Kingston_AUS</t>
+  </si>
+  <si>
+    <t>en_battery_8h_Kingston_AUS</t>
+  </si>
+  <si>
     <t>en_battery_4h_PortHedland_AUS</t>
   </si>
   <si>
     <t>en_battery_8h_PortHedland_AUS</t>
   </si>
   <si>
-    <t>en_battery_4h_Hobart_AUS</t>
-  </si>
-  <si>
-    <t>en_battery_8h_Hobart_AUS</t>
-  </si>
-  <si>
     <t>en_battery_4h_Kalgoorlie_AUS</t>
   </si>
   <si>
@@ -5568,12 +5568,6 @@
   </si>
   <si>
     <t>elc_won_AUS_097</t>
-  </si>
-  <si>
-    <t>START</t>
-  </si>
-  <si>
-    <t>bio*</t>
   </si>
 </sst>
 </file>
@@ -6048,7 +6042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456E1EC7-2E61-4DC3-B37B-7E050A1433CE}">
-  <dimension ref="B2:J12"/>
+  <dimension ref="B2:I11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -6056,17 +6050,16 @@
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>22</v>
       </c>
@@ -6083,13 +6076,10 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>26</v>
       </c>
@@ -6100,14 +6090,14 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <f>J4*3.6</f>
+        <f>I4*3.6</f>
         <v>338.40000000000003</v>
       </c>
-      <c r="J4">
+      <c r="I4">
         <v>94</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -6118,14 +6108,14 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <f>J5*3.6</f>
+        <f>I5*3.6</f>
         <v>198</v>
       </c>
-      <c r="J5">
+      <c r="I5">
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>26</v>
       </c>
@@ -6136,14 +6126,14 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <f>J6*3.6</f>
+        <f>I6*3.6</f>
         <v>252</v>
       </c>
-      <c r="J6">
+      <c r="I6">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -6157,7 +6147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>29</v>
       </c>
@@ -6171,7 +6161,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>34</v>
       </c>
@@ -6186,37 +6176,26 @@
         <v>co2captured</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="E10">
         <v>50</v>
       </c>
-      <c r="H10" t="s">
+      <c r="G10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>51</v>
       </c>
       <c r="E11">
         <v>8.76</v>
       </c>
-      <c r="H11" t="s">
+      <c r="G11" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E12">
-        <v>2100</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1831</v>
       </c>
     </row>
   </sheetData>
@@ -6226,7 +6205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F11348-C968-4282-91F8-E95962193F0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A66F8A8-0780-436A-8BC5-057B5F1E02C6}">
   <dimension ref="B2:AG1199"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6302,13 +6281,13 @@
         <v>113</v>
       </c>
       <c r="C4">
-        <v>0.77420073022117442</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D4">
-        <v>408.1</v>
+        <v>99.000000000000014</v>
       </c>
       <c r="E4">
-        <v>0.97774000000000005</v>
+        <v>0.99460000000000004</v>
       </c>
       <c r="H4" t="s">
         <v>170</v>
@@ -6317,7 +6296,7 @@
         <v>171</v>
       </c>
       <c r="J4">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K4" t="s">
         <v>172</v>
@@ -6373,13 +6352,13 @@
         <v>114</v>
       </c>
       <c r="C5">
-        <v>1.5484014604423488</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D5">
-        <v>99.000000000000014</v>
+        <v>408.1</v>
       </c>
       <c r="E5">
-        <v>0.99460000000000004</v>
+        <v>0.97774000000000005</v>
       </c>
       <c r="H5" t="s">
         <v>170</v>
@@ -6388,7 +6367,7 @@
         <v>173</v>
       </c>
       <c r="J5">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K5" t="s">
         <v>172</v>
@@ -6456,7 +6435,7 @@
         <v>174</v>
       </c>
       <c r="J6">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K6" t="s">
         <v>172</v>
@@ -6521,7 +6500,7 @@
         <v>171</v>
       </c>
       <c r="J7">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K7" t="s">
         <v>172</v>
@@ -6571,7 +6550,7 @@
         <v>173</v>
       </c>
       <c r="J8">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K8" t="s">
         <v>172</v>
@@ -6621,7 +6600,7 @@
         <v>174</v>
       </c>
       <c r="J9">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K9" t="s">
         <v>172</v>
@@ -6671,7 +6650,7 @@
         <v>171</v>
       </c>
       <c r="J10">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K10" t="s">
         <v>172</v>
@@ -6721,7 +6700,7 @@
         <v>173</v>
       </c>
       <c r="J11">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K11" t="s">
         <v>172</v>
@@ -6771,7 +6750,7 @@
         <v>174</v>
       </c>
       <c r="J12">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K12" t="s">
         <v>172</v>
@@ -6821,7 +6800,7 @@
         <v>171</v>
       </c>
       <c r="J13">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K13" t="s">
         <v>172</v>
@@ -6871,7 +6850,7 @@
         <v>173</v>
       </c>
       <c r="J14">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K14" t="s">
         <v>172</v>
@@ -6921,7 +6900,7 @@
         <v>174</v>
       </c>
       <c r="J15">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K15" t="s">
         <v>172</v>
@@ -6971,7 +6950,7 @@
         <v>171</v>
       </c>
       <c r="J16">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K16" t="s">
         <v>172</v>
@@ -7021,7 +7000,7 @@
         <v>173</v>
       </c>
       <c r="J17">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K17" t="s">
         <v>172</v>
@@ -7071,7 +7050,7 @@
         <v>174</v>
       </c>
       <c r="J18">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K18" t="s">
         <v>172</v>
@@ -7121,7 +7100,7 @@
         <v>171</v>
       </c>
       <c r="J19">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K19" t="s">
         <v>172</v>
@@ -7171,7 +7150,7 @@
         <v>173</v>
       </c>
       <c r="J20">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K20" t="s">
         <v>172</v>
@@ -7221,7 +7200,7 @@
         <v>174</v>
       </c>
       <c r="J21">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K21" t="s">
         <v>172</v>
@@ -7271,7 +7250,7 @@
         <v>171</v>
       </c>
       <c r="J22">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K22" t="s">
         <v>172</v>
@@ -7321,7 +7300,7 @@
         <v>173</v>
       </c>
       <c r="J23">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K23" t="s">
         <v>172</v>
@@ -7371,7 +7350,7 @@
         <v>174</v>
       </c>
       <c r="J24">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K24" t="s">
         <v>172</v>
@@ -7421,7 +7400,7 @@
         <v>171</v>
       </c>
       <c r="J25">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K25" t="s">
         <v>172</v>
@@ -7471,7 +7450,7 @@
         <v>173</v>
       </c>
       <c r="J26">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K26" t="s">
         <v>172</v>
@@ -7521,7 +7500,7 @@
         <v>174</v>
       </c>
       <c r="J27">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K27" t="s">
         <v>172</v>
@@ -7571,7 +7550,7 @@
         <v>171</v>
       </c>
       <c r="J28">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K28" t="s">
         <v>172</v>
@@ -7606,13 +7585,13 @@
         <v>138</v>
       </c>
       <c r="C29">
-        <v>1.3763568537265327</v>
+        <v>0.34408921343163318</v>
       </c>
       <c r="D29">
-        <v>157.30000000000001</v>
+        <v>279.40000000000003</v>
       </c>
       <c r="E29">
-        <v>0.99141999999999997</v>
+        <v>0.98475999999999997</v>
       </c>
       <c r="H29" t="s">
         <v>182</v>
@@ -7621,7 +7600,7 @@
         <v>173</v>
       </c>
       <c r="J29">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K29" t="s">
         <v>172</v>
@@ -7659,10 +7638,10 @@
         <v>0.34408921343163318</v>
       </c>
       <c r="D30">
-        <v>279.40000000000003</v>
+        <v>437.8</v>
       </c>
       <c r="E30">
-        <v>0.98475999999999997</v>
+        <v>0.97611999999999999</v>
       </c>
       <c r="H30" t="s">
         <v>182</v>
@@ -7671,7 +7650,7 @@
         <v>174</v>
       </c>
       <c r="J30">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K30" t="s">
         <v>172</v>
@@ -7706,13 +7685,13 @@
         <v>140</v>
       </c>
       <c r="C31">
-        <v>0.34408921343163318</v>
+        <v>0.77420073022117442</v>
       </c>
       <c r="D31">
-        <v>437.8</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="E31">
-        <v>0.97611999999999999</v>
+        <v>0.99292000000000002</v>
       </c>
       <c r="H31" t="s">
         <v>183</v>
@@ -7721,7 +7700,7 @@
         <v>171</v>
       </c>
       <c r="J31">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K31" t="s">
         <v>172</v>
@@ -7756,13 +7735,13 @@
         <v>141</v>
       </c>
       <c r="C32">
-        <v>0.77420073022117442</v>
+        <v>4.6764852189117416</v>
       </c>
       <c r="D32">
-        <v>129.80000000000001</v>
+        <v>305.8</v>
       </c>
       <c r="E32">
-        <v>0.99292000000000002</v>
+        <v>0.98331999999999997</v>
       </c>
       <c r="H32" t="s">
         <v>183</v>
@@ -7771,7 +7750,7 @@
         <v>173</v>
       </c>
       <c r="J32">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K32" t="s">
         <v>172</v>
@@ -7806,13 +7785,13 @@
         <v>142</v>
       </c>
       <c r="C33">
-        <v>4.6764852189117416</v>
+        <v>3.2688475276005144</v>
       </c>
       <c r="D33">
-        <v>305.8</v>
+        <v>537.90000000000009</v>
       </c>
       <c r="E33">
-        <v>0.98331999999999997</v>
+        <v>0.97065999999999997</v>
       </c>
       <c r="H33" t="s">
         <v>183</v>
@@ -7821,7 +7800,7 @@
         <v>174</v>
       </c>
       <c r="J33">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K33" t="s">
         <v>172</v>
@@ -7856,13 +7835,13 @@
         <v>143</v>
       </c>
       <c r="C34">
-        <v>3.2688475276005144</v>
+        <v>0.64516727518431216</v>
       </c>
       <c r="D34">
-        <v>537.90000000000009</v>
+        <v>245.3</v>
       </c>
       <c r="E34">
-        <v>0.97065999999999997</v>
+        <v>0.98662000000000005</v>
       </c>
       <c r="H34" t="s">
         <v>184</v>
@@ -7871,7 +7850,7 @@
         <v>171</v>
       </c>
       <c r="J34">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K34" t="s">
         <v>172</v>
@@ -7906,13 +7885,13 @@
         <v>144</v>
       </c>
       <c r="C35">
-        <v>0.64516727518431216</v>
+        <v>2.5806691007372482</v>
       </c>
       <c r="D35">
-        <v>245.3</v>
+        <v>74.800000000000011</v>
       </c>
       <c r="E35">
-        <v>0.98662000000000005</v>
+        <v>0.99592000000000003</v>
       </c>
       <c r="H35" t="s">
         <v>184</v>
@@ -7921,7 +7900,7 @@
         <v>173</v>
       </c>
       <c r="J35">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K35" t="s">
         <v>172</v>
@@ -7956,13 +7935,13 @@
         <v>145</v>
       </c>
       <c r="C36">
-        <v>2.5806691007372482</v>
+        <v>1.2903345503686237</v>
       </c>
       <c r="D36">
-        <v>74.800000000000011</v>
+        <v>135.30000000000001</v>
       </c>
       <c r="E36">
-        <v>0.99592000000000003</v>
+        <v>0.99261999999999995</v>
       </c>
       <c r="H36" t="s">
         <v>184</v>
@@ -7971,7 +7950,7 @@
         <v>174</v>
       </c>
       <c r="J36">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K36" t="s">
         <v>172</v>
@@ -8006,13 +7985,13 @@
         <v>146</v>
       </c>
       <c r="C37">
-        <v>1.2903345503686237</v>
+        <v>1.7204460671581658</v>
       </c>
       <c r="D37">
-        <v>135.30000000000001</v>
+        <v>85.800000000000011</v>
       </c>
       <c r="E37">
-        <v>0.99261999999999995</v>
+        <v>0.99531999999999998</v>
       </c>
       <c r="H37" t="s">
         <v>185</v>
@@ -8021,7 +8000,7 @@
         <v>171</v>
       </c>
       <c r="J37">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K37" t="s">
         <v>172</v>
@@ -8071,7 +8050,7 @@
         <v>173</v>
       </c>
       <c r="J38">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K38" t="s">
         <v>172</v>
@@ -8121,7 +8100,7 @@
         <v>174</v>
       </c>
       <c r="J39">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K39" t="s">
         <v>172</v>
@@ -8171,7 +8150,7 @@
         <v>171</v>
       </c>
       <c r="J40">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K40" t="s">
         <v>172</v>
@@ -8221,7 +8200,7 @@
         <v>173</v>
       </c>
       <c r="J41">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K41" t="s">
         <v>172</v>
@@ -8271,7 +8250,7 @@
         <v>174</v>
       </c>
       <c r="J42">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K42" t="s">
         <v>172</v>
@@ -8321,7 +8300,7 @@
         <v>171</v>
       </c>
       <c r="J43">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K43" t="s">
         <v>172</v>
@@ -8371,7 +8350,7 @@
         <v>173</v>
       </c>
       <c r="J44">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K44" t="s">
         <v>172</v>
@@ -8421,7 +8400,7 @@
         <v>174</v>
       </c>
       <c r="J45">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K45" t="s">
         <v>172</v>
@@ -8471,7 +8450,7 @@
         <v>171</v>
       </c>
       <c r="J46">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K46" t="s">
         <v>172</v>
@@ -8521,7 +8500,7 @@
         <v>173</v>
       </c>
       <c r="J47">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K47" t="s">
         <v>172</v>
@@ -8571,7 +8550,7 @@
         <v>174</v>
       </c>
       <c r="J48">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K48" t="s">
         <v>172</v>
@@ -8606,13 +8585,13 @@
         <v>158</v>
       </c>
       <c r="C49">
-        <v>5.8065054766588062</v>
+        <v>1.5484014604423488</v>
       </c>
       <c r="D49">
-        <v>138.60000000000002</v>
+        <v>119.9</v>
       </c>
       <c r="E49">
-        <v>0.99243999999999999</v>
+        <v>0.99346000000000001</v>
       </c>
       <c r="H49" t="s">
         <v>189</v>
@@ -8621,7 +8600,7 @@
         <v>171</v>
       </c>
       <c r="J49">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K49" t="s">
         <v>172</v>
@@ -8656,13 +8635,13 @@
         <v>159</v>
       </c>
       <c r="C50">
-        <v>1.5484014604423488</v>
+        <v>5.8065054766588062</v>
       </c>
       <c r="D50">
-        <v>119.9</v>
+        <v>138.60000000000002</v>
       </c>
       <c r="E50">
-        <v>0.99346000000000001</v>
+        <v>0.99243999999999999</v>
       </c>
       <c r="H50" t="s">
         <v>189</v>
@@ -8671,7 +8650,7 @@
         <v>173</v>
       </c>
       <c r="J50">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K50" t="s">
         <v>172</v>
@@ -8721,7 +8700,7 @@
         <v>174</v>
       </c>
       <c r="J51">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K51" t="s">
         <v>172</v>
@@ -8771,7 +8750,7 @@
         <v>171</v>
       </c>
       <c r="J52">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K52" t="s">
         <v>172</v>
@@ -8821,7 +8800,7 @@
         <v>173</v>
       </c>
       <c r="J53">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K53" t="s">
         <v>172</v>
@@ -8871,7 +8850,7 @@
         <v>174</v>
       </c>
       <c r="J54">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K54" t="s">
         <v>172</v>
@@ -8921,7 +8900,7 @@
         <v>171</v>
       </c>
       <c r="J55">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K55" t="s">
         <v>172</v>
@@ -8971,7 +8950,7 @@
         <v>173</v>
       </c>
       <c r="J56">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K56" t="s">
         <v>172</v>
@@ -9021,7 +9000,7 @@
         <v>174</v>
       </c>
       <c r="J57">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K57" t="s">
         <v>172</v>
@@ -9059,7 +9038,7 @@
         <v>171</v>
       </c>
       <c r="J58">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K58" t="s">
         <v>172</v>
@@ -9097,7 +9076,7 @@
         <v>173</v>
       </c>
       <c r="J59">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K59" t="s">
         <v>172</v>
@@ -9135,7 +9114,7 @@
         <v>174</v>
       </c>
       <c r="J60">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K60" t="s">
         <v>172</v>
@@ -9173,7 +9152,7 @@
         <v>171</v>
       </c>
       <c r="J61">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K61" t="s">
         <v>172</v>
@@ -9211,7 +9190,7 @@
         <v>173</v>
       </c>
       <c r="J62">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K62" t="s">
         <v>172</v>
@@ -9249,7 +9228,7 @@
         <v>174</v>
       </c>
       <c r="J63">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K63" t="s">
         <v>172</v>
@@ -9287,7 +9266,7 @@
         <v>171</v>
       </c>
       <c r="J64">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K64" t="s">
         <v>172</v>
@@ -9325,7 +9304,7 @@
         <v>173</v>
       </c>
       <c r="J65">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K65" t="s">
         <v>172</v>
@@ -9363,7 +9342,7 @@
         <v>174</v>
       </c>
       <c r="J66">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K66" t="s">
         <v>172</v>
@@ -9401,7 +9380,7 @@
         <v>171</v>
       </c>
       <c r="J67">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K67" t="s">
         <v>172</v>
@@ -9439,7 +9418,7 @@
         <v>173</v>
       </c>
       <c r="J68">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K68" t="s">
         <v>172</v>
@@ -9477,7 +9456,7 @@
         <v>174</v>
       </c>
       <c r="J69">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K69" t="s">
         <v>172</v>
@@ -9515,7 +9494,7 @@
         <v>171</v>
       </c>
       <c r="J70">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K70" t="s">
         <v>172</v>
@@ -9553,7 +9532,7 @@
         <v>173</v>
       </c>
       <c r="J71">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K71" t="s">
         <v>172</v>
@@ -9591,7 +9570,7 @@
         <v>174</v>
       </c>
       <c r="J72">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K72" t="s">
         <v>172</v>
@@ -9629,7 +9608,7 @@
         <v>171</v>
       </c>
       <c r="J73">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K73" t="s">
         <v>172</v>
@@ -9667,7 +9646,7 @@
         <v>173</v>
       </c>
       <c r="J74">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K74" t="s">
         <v>172</v>
@@ -9705,7 +9684,7 @@
         <v>174</v>
       </c>
       <c r="J75">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K75" t="s">
         <v>172</v>
@@ -9743,7 +9722,7 @@
         <v>171</v>
       </c>
       <c r="J76">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K76" t="s">
         <v>172</v>
@@ -9781,7 +9760,7 @@
         <v>173</v>
       </c>
       <c r="J77">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K77" t="s">
         <v>172</v>
@@ -9819,7 +9798,7 @@
         <v>174</v>
       </c>
       <c r="J78">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K78" t="s">
         <v>172</v>
@@ -9857,7 +9836,7 @@
         <v>171</v>
       </c>
       <c r="J79">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K79" t="s">
         <v>172</v>
@@ -9895,7 +9874,7 @@
         <v>173</v>
       </c>
       <c r="J80">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K80" t="s">
         <v>172</v>
@@ -9933,7 +9912,7 @@
         <v>174</v>
       </c>
       <c r="J81">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K81" t="s">
         <v>172</v>
@@ -9971,7 +9950,7 @@
         <v>171</v>
       </c>
       <c r="J82">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K82" t="s">
         <v>172</v>
@@ -10009,7 +9988,7 @@
         <v>173</v>
       </c>
       <c r="J83">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K83" t="s">
         <v>172</v>
@@ -10047,7 +10026,7 @@
         <v>174</v>
       </c>
       <c r="J84">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K84" t="s">
         <v>172</v>
@@ -10085,7 +10064,7 @@
         <v>171</v>
       </c>
       <c r="J85">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K85" t="s">
         <v>172</v>
@@ -10123,7 +10102,7 @@
         <v>173</v>
       </c>
       <c r="J86">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K86" t="s">
         <v>172</v>
@@ -10161,7 +10140,7 @@
         <v>174</v>
       </c>
       <c r="J87">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K87" t="s">
         <v>172</v>
@@ -10199,7 +10178,7 @@
         <v>171</v>
       </c>
       <c r="J88">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K88" t="s">
         <v>172</v>
@@ -10237,7 +10216,7 @@
         <v>173</v>
       </c>
       <c r="J89">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K89" t="s">
         <v>172</v>
@@ -10275,7 +10254,7 @@
         <v>174</v>
       </c>
       <c r="J90">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K90" t="s">
         <v>172</v>
@@ -10313,7 +10292,7 @@
         <v>171</v>
       </c>
       <c r="J91">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K91" t="s">
         <v>172</v>
@@ -10351,7 +10330,7 @@
         <v>173</v>
       </c>
       <c r="J92">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K92" t="s">
         <v>172</v>
@@ -10389,7 +10368,7 @@
         <v>174</v>
       </c>
       <c r="J93">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K93" t="s">
         <v>172</v>
@@ -10427,7 +10406,7 @@
         <v>171</v>
       </c>
       <c r="J94">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K94" t="s">
         <v>172</v>
@@ -10465,7 +10444,7 @@
         <v>173</v>
       </c>
       <c r="J95">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K95" t="s">
         <v>172</v>
@@ -10503,7 +10482,7 @@
         <v>174</v>
       </c>
       <c r="J96">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K96" t="s">
         <v>172</v>
@@ -10541,7 +10520,7 @@
         <v>171</v>
       </c>
       <c r="J97">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K97" t="s">
         <v>172</v>
@@ -10579,7 +10558,7 @@
         <v>173</v>
       </c>
       <c r="J98">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K98" t="s">
         <v>172</v>
@@ -10617,7 +10596,7 @@
         <v>174</v>
       </c>
       <c r="J99">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K99" t="s">
         <v>172</v>
@@ -10655,7 +10634,7 @@
         <v>171</v>
       </c>
       <c r="J100">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K100" t="s">
         <v>172</v>
@@ -10693,7 +10672,7 @@
         <v>173</v>
       </c>
       <c r="J101">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K101" t="s">
         <v>172</v>
@@ -10731,7 +10710,7 @@
         <v>174</v>
       </c>
       <c r="J102">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K102" t="s">
         <v>172</v>
@@ -10769,7 +10748,7 @@
         <v>171</v>
       </c>
       <c r="J103">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K103" t="s">
         <v>172</v>
@@ -10807,7 +10786,7 @@
         <v>173</v>
       </c>
       <c r="J104">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K104" t="s">
         <v>172</v>
@@ -10845,7 +10824,7 @@
         <v>174</v>
       </c>
       <c r="J105">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K105" t="s">
         <v>172</v>
@@ -10883,7 +10862,7 @@
         <v>171</v>
       </c>
       <c r="J106">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K106" t="s">
         <v>172</v>
@@ -10921,7 +10900,7 @@
         <v>173</v>
       </c>
       <c r="J107">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K107" t="s">
         <v>172</v>
@@ -10959,7 +10938,7 @@
         <v>174</v>
       </c>
       <c r="J108">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K108" t="s">
         <v>172</v>
@@ -10997,7 +10976,7 @@
         <v>171</v>
       </c>
       <c r="J109">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K109" t="s">
         <v>172</v>
@@ -11035,7 +11014,7 @@
         <v>173</v>
       </c>
       <c r="J110">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K110" t="s">
         <v>172</v>
@@ -11073,7 +11052,7 @@
         <v>174</v>
       </c>
       <c r="J111">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K111" t="s">
         <v>172</v>
@@ -11111,7 +11090,7 @@
         <v>171</v>
       </c>
       <c r="J112">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K112" t="s">
         <v>172</v>
@@ -11149,7 +11128,7 @@
         <v>173</v>
       </c>
       <c r="J113">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K113" t="s">
         <v>172</v>
@@ -11187,7 +11166,7 @@
         <v>174</v>
       </c>
       <c r="J114">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K114" t="s">
         <v>172</v>
@@ -11225,7 +11204,7 @@
         <v>171</v>
       </c>
       <c r="J115">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K115" t="s">
         <v>172</v>
@@ -11263,7 +11242,7 @@
         <v>173</v>
       </c>
       <c r="J116">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K116" t="s">
         <v>172</v>
@@ -11301,7 +11280,7 @@
         <v>174</v>
       </c>
       <c r="J117">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K117" t="s">
         <v>172</v>
@@ -11339,7 +11318,7 @@
         <v>171</v>
       </c>
       <c r="J118">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K118" t="s">
         <v>172</v>
@@ -11377,7 +11356,7 @@
         <v>173</v>
       </c>
       <c r="J119">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K119" t="s">
         <v>172</v>
@@ -11415,7 +11394,7 @@
         <v>174</v>
       </c>
       <c r="J120">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K120" t="s">
         <v>172</v>
@@ -11453,7 +11432,7 @@
         <v>171</v>
       </c>
       <c r="J121">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K121" t="s">
         <v>172</v>
@@ -11491,7 +11470,7 @@
         <v>173</v>
       </c>
       <c r="J122">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K122" t="s">
         <v>172</v>
@@ -11529,7 +11508,7 @@
         <v>174</v>
       </c>
       <c r="J123">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K123" t="s">
         <v>172</v>
@@ -11567,7 +11546,7 @@
         <v>171</v>
       </c>
       <c r="J124">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K124" t="s">
         <v>172</v>
@@ -11605,7 +11584,7 @@
         <v>173</v>
       </c>
       <c r="J125">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K125" t="s">
         <v>172</v>
@@ -11643,7 +11622,7 @@
         <v>174</v>
       </c>
       <c r="J126">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K126" t="s">
         <v>172</v>
@@ -11681,7 +11660,7 @@
         <v>171</v>
       </c>
       <c r="J127">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K127" t="s">
         <v>172</v>
@@ -11719,7 +11698,7 @@
         <v>173</v>
       </c>
       <c r="J128">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K128" t="s">
         <v>172</v>
@@ -11757,7 +11736,7 @@
         <v>174</v>
       </c>
       <c r="J129">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K129" t="s">
         <v>172</v>
@@ -11795,7 +11774,7 @@
         <v>171</v>
       </c>
       <c r="J130">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K130" t="s">
         <v>172</v>
@@ -11833,7 +11812,7 @@
         <v>173</v>
       </c>
       <c r="J131">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K131" t="s">
         <v>172</v>
@@ -11871,7 +11850,7 @@
         <v>174</v>
       </c>
       <c r="J132">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K132" t="s">
         <v>172</v>
@@ -11909,7 +11888,7 @@
         <v>171</v>
       </c>
       <c r="J133">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K133" t="s">
         <v>172</v>
@@ -11947,7 +11926,7 @@
         <v>173</v>
       </c>
       <c r="J134">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K134" t="s">
         <v>172</v>
@@ -11985,7 +11964,7 @@
         <v>174</v>
       </c>
       <c r="J135">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K135" t="s">
         <v>172</v>
@@ -12023,7 +12002,7 @@
         <v>171</v>
       </c>
       <c r="J136">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K136" t="s">
         <v>172</v>
@@ -12061,7 +12040,7 @@
         <v>173</v>
       </c>
       <c r="J137">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K137" t="s">
         <v>172</v>
@@ -12099,7 +12078,7 @@
         <v>174</v>
       </c>
       <c r="J138">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K138" t="s">
         <v>172</v>
@@ -12137,7 +12116,7 @@
         <v>171</v>
       </c>
       <c r="J139">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K139" t="s">
         <v>172</v>
@@ -12175,7 +12154,7 @@
         <v>173</v>
       </c>
       <c r="J140">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K140" t="s">
         <v>172</v>
@@ -12213,7 +12192,7 @@
         <v>174</v>
       </c>
       <c r="J141">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K141" t="s">
         <v>172</v>
@@ -12251,7 +12230,7 @@
         <v>171</v>
       </c>
       <c r="J142">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K142" t="s">
         <v>172</v>
@@ -12289,7 +12268,7 @@
         <v>173</v>
       </c>
       <c r="J143">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K143" t="s">
         <v>172</v>
@@ -12327,7 +12306,7 @@
         <v>174</v>
       </c>
       <c r="J144">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K144" t="s">
         <v>172</v>
@@ -12365,7 +12344,7 @@
         <v>171</v>
       </c>
       <c r="J145">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K145" t="s">
         <v>172</v>
@@ -12403,7 +12382,7 @@
         <v>173</v>
       </c>
       <c r="J146">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K146" t="s">
         <v>172</v>
@@ -12441,7 +12420,7 @@
         <v>174</v>
       </c>
       <c r="J147">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K147" t="s">
         <v>172</v>
@@ -12479,7 +12458,7 @@
         <v>171</v>
       </c>
       <c r="J148">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K148" t="s">
         <v>172</v>
@@ -12517,7 +12496,7 @@
         <v>173</v>
       </c>
       <c r="J149">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K149" t="s">
         <v>172</v>
@@ -12555,7 +12534,7 @@
         <v>174</v>
       </c>
       <c r="J150">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K150" t="s">
         <v>172</v>
@@ -12593,7 +12572,7 @@
         <v>171</v>
       </c>
       <c r="J151">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K151" t="s">
         <v>172</v>
@@ -12631,7 +12610,7 @@
         <v>173</v>
       </c>
       <c r="J152">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K152" t="s">
         <v>172</v>
@@ -12669,7 +12648,7 @@
         <v>174</v>
       </c>
       <c r="J153">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K153" t="s">
         <v>172</v>
@@ -12707,7 +12686,7 @@
         <v>171</v>
       </c>
       <c r="J154">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K154" t="s">
         <v>172</v>
@@ -12745,7 +12724,7 @@
         <v>173</v>
       </c>
       <c r="J155">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K155" t="s">
         <v>172</v>
@@ -12783,7 +12762,7 @@
         <v>174</v>
       </c>
       <c r="J156">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K156" t="s">
         <v>172</v>
@@ -12821,7 +12800,7 @@
         <v>171</v>
       </c>
       <c r="J157">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K157" t="s">
         <v>172</v>
@@ -12859,7 +12838,7 @@
         <v>173</v>
       </c>
       <c r="J158">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K158" t="s">
         <v>172</v>
@@ -12897,7 +12876,7 @@
         <v>174</v>
       </c>
       <c r="J159">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K159" t="s">
         <v>172</v>
@@ -12935,7 +12914,7 @@
         <v>171</v>
       </c>
       <c r="J160">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K160" t="s">
         <v>172</v>
@@ -12973,7 +12952,7 @@
         <v>173</v>
       </c>
       <c r="J161">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K161" t="s">
         <v>172</v>
@@ -13011,7 +12990,7 @@
         <v>174</v>
       </c>
       <c r="J162">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K162" t="s">
         <v>172</v>
@@ -13049,7 +13028,7 @@
         <v>171</v>
       </c>
       <c r="J163">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K163" t="s">
         <v>172</v>
@@ -13087,7 +13066,7 @@
         <v>173</v>
       </c>
       <c r="J164">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K164" t="s">
         <v>172</v>
@@ -13125,7 +13104,7 @@
         <v>174</v>
       </c>
       <c r="J165">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K165" t="s">
         <v>172</v>
@@ -13163,7 +13142,7 @@
         <v>171</v>
       </c>
       <c r="J166">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K166" t="s">
         <v>172</v>
@@ -13201,7 +13180,7 @@
         <v>173</v>
       </c>
       <c r="J167">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K167" t="s">
         <v>172</v>
@@ -13239,7 +13218,7 @@
         <v>174</v>
       </c>
       <c r="J168">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K168" t="s">
         <v>172</v>
@@ -13277,7 +13256,7 @@
         <v>171</v>
       </c>
       <c r="J169">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K169" t="s">
         <v>172</v>
@@ -13315,7 +13294,7 @@
         <v>173</v>
       </c>
       <c r="J170">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K170" t="s">
         <v>172</v>
@@ -13353,7 +13332,7 @@
         <v>174</v>
       </c>
       <c r="J171">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K171" t="s">
         <v>172</v>
@@ -13391,7 +13370,7 @@
         <v>171</v>
       </c>
       <c r="J172">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K172" t="s">
         <v>172</v>
@@ -13429,7 +13408,7 @@
         <v>173</v>
       </c>
       <c r="J173">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K173" t="s">
         <v>172</v>
@@ -13467,7 +13446,7 @@
         <v>174</v>
       </c>
       <c r="J174">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K174" t="s">
         <v>172</v>
@@ -13505,7 +13484,7 @@
         <v>171</v>
       </c>
       <c r="J175">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K175" t="s">
         <v>172</v>
@@ -13543,7 +13522,7 @@
         <v>173</v>
       </c>
       <c r="J176">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K176" t="s">
         <v>172</v>
@@ -13581,7 +13560,7 @@
         <v>174</v>
       </c>
       <c r="J177">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K177" t="s">
         <v>172</v>
@@ -13607,7 +13586,7 @@
         <v>171</v>
       </c>
       <c r="J178">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K178" t="s">
         <v>172</v>
@@ -13633,7 +13612,7 @@
         <v>173</v>
       </c>
       <c r="J179">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K179" t="s">
         <v>172</v>
@@ -13659,7 +13638,7 @@
         <v>174</v>
       </c>
       <c r="J180">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K180" t="s">
         <v>172</v>
@@ -13685,7 +13664,7 @@
         <v>171</v>
       </c>
       <c r="J181">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K181" t="s">
         <v>172</v>
@@ -13711,7 +13690,7 @@
         <v>173</v>
       </c>
       <c r="J182">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K182" t="s">
         <v>172</v>
@@ -13737,7 +13716,7 @@
         <v>174</v>
       </c>
       <c r="J183">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K183" t="s">
         <v>172</v>
@@ -13763,7 +13742,7 @@
         <v>171</v>
       </c>
       <c r="J184">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K184" t="s">
         <v>172</v>
@@ -13789,7 +13768,7 @@
         <v>173</v>
       </c>
       <c r="J185">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K185" t="s">
         <v>172</v>
@@ -13815,7 +13794,7 @@
         <v>174</v>
       </c>
       <c r="J186">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K186" t="s">
         <v>172</v>
@@ -13841,7 +13820,7 @@
         <v>171</v>
       </c>
       <c r="J187">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K187" t="s">
         <v>172</v>
@@ -13867,7 +13846,7 @@
         <v>173</v>
       </c>
       <c r="J188">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K188" t="s">
         <v>172</v>
@@ -13893,7 +13872,7 @@
         <v>174</v>
       </c>
       <c r="J189">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K189" t="s">
         <v>172</v>
@@ -13919,7 +13898,7 @@
         <v>171</v>
       </c>
       <c r="J190">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K190" t="s">
         <v>172</v>
@@ -13945,7 +13924,7 @@
         <v>173</v>
       </c>
       <c r="J191">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K191" t="s">
         <v>172</v>
@@ -13971,7 +13950,7 @@
         <v>174</v>
       </c>
       <c r="J192">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K192" t="s">
         <v>172</v>
@@ -13997,7 +13976,7 @@
         <v>171</v>
       </c>
       <c r="J193">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K193" t="s">
         <v>172</v>
@@ -14023,7 +14002,7 @@
         <v>173</v>
       </c>
       <c r="J194">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K194" t="s">
         <v>172</v>
@@ -14049,7 +14028,7 @@
         <v>174</v>
       </c>
       <c r="J195">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K195" t="s">
         <v>172</v>
@@ -14075,7 +14054,7 @@
         <v>171</v>
       </c>
       <c r="J196">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K196" t="s">
         <v>172</v>
@@ -14101,7 +14080,7 @@
         <v>173</v>
       </c>
       <c r="J197">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K197" t="s">
         <v>172</v>
@@ -14127,7 +14106,7 @@
         <v>174</v>
       </c>
       <c r="J198">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K198" t="s">
         <v>172</v>
@@ -14153,7 +14132,7 @@
         <v>171</v>
       </c>
       <c r="J199">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K199" t="s">
         <v>172</v>
@@ -14179,7 +14158,7 @@
         <v>173</v>
       </c>
       <c r="J200">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K200" t="s">
         <v>172</v>
@@ -14205,7 +14184,7 @@
         <v>174</v>
       </c>
       <c r="J201">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K201" t="s">
         <v>172</v>
@@ -14231,7 +14210,7 @@
         <v>171</v>
       </c>
       <c r="J202">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K202" t="s">
         <v>172</v>
@@ -14257,7 +14236,7 @@
         <v>173</v>
       </c>
       <c r="J203">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K203" t="s">
         <v>172</v>
@@ -14283,7 +14262,7 @@
         <v>174</v>
       </c>
       <c r="J204">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K204" t="s">
         <v>172</v>
@@ -14309,7 +14288,7 @@
         <v>171</v>
       </c>
       <c r="J205">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K205" t="s">
         <v>172</v>
@@ -14335,7 +14314,7 @@
         <v>173</v>
       </c>
       <c r="J206">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K206" t="s">
         <v>172</v>
@@ -14361,7 +14340,7 @@
         <v>174</v>
       </c>
       <c r="J207">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K207" t="s">
         <v>172</v>
@@ -14387,7 +14366,7 @@
         <v>171</v>
       </c>
       <c r="J208">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K208" t="s">
         <v>172</v>
@@ -14413,7 +14392,7 @@
         <v>173</v>
       </c>
       <c r="J209">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K209" t="s">
         <v>172</v>
@@ -14439,7 +14418,7 @@
         <v>174</v>
       </c>
       <c r="J210">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K210" t="s">
         <v>172</v>
@@ -14465,7 +14444,7 @@
         <v>171</v>
       </c>
       <c r="J211">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K211" t="s">
         <v>172</v>
@@ -14491,7 +14470,7 @@
         <v>173</v>
       </c>
       <c r="J212">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K212" t="s">
         <v>172</v>
@@ -14517,7 +14496,7 @@
         <v>174</v>
       </c>
       <c r="J213">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K213" t="s">
         <v>172</v>
@@ -14543,7 +14522,7 @@
         <v>171</v>
       </c>
       <c r="J214">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K214" t="s">
         <v>172</v>
@@ -14569,7 +14548,7 @@
         <v>173</v>
       </c>
       <c r="J215">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K215" t="s">
         <v>172</v>
@@ -14595,7 +14574,7 @@
         <v>174</v>
       </c>
       <c r="J216">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K216" t="s">
         <v>172</v>
@@ -14621,7 +14600,7 @@
         <v>171</v>
       </c>
       <c r="J217">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K217" t="s">
         <v>172</v>
@@ -14647,7 +14626,7 @@
         <v>173</v>
       </c>
       <c r="J218">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K218" t="s">
         <v>172</v>
@@ -14673,7 +14652,7 @@
         <v>174</v>
       </c>
       <c r="J219">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K219" t="s">
         <v>172</v>
@@ -14699,7 +14678,7 @@
         <v>171</v>
       </c>
       <c r="J220">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K220" t="s">
         <v>172</v>
@@ -14725,7 +14704,7 @@
         <v>173</v>
       </c>
       <c r="J221">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K221" t="s">
         <v>172</v>
@@ -14751,7 +14730,7 @@
         <v>174</v>
       </c>
       <c r="J222">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K222" t="s">
         <v>172</v>
@@ -14777,7 +14756,7 @@
         <v>171</v>
       </c>
       <c r="J223">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K223" t="s">
         <v>172</v>
@@ -14803,7 +14782,7 @@
         <v>173</v>
       </c>
       <c r="J224">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K224" t="s">
         <v>172</v>
@@ -14829,7 +14808,7 @@
         <v>174</v>
       </c>
       <c r="J225">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K225" t="s">
         <v>172</v>
@@ -14855,7 +14834,7 @@
         <v>171</v>
       </c>
       <c r="J226">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K226" t="s">
         <v>172</v>
@@ -14881,7 +14860,7 @@
         <v>173</v>
       </c>
       <c r="J227">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K227" t="s">
         <v>172</v>
@@ -14907,7 +14886,7 @@
         <v>174</v>
       </c>
       <c r="J228">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K228" t="s">
         <v>172</v>
@@ -14933,7 +14912,7 @@
         <v>171</v>
       </c>
       <c r="J229">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K229" t="s">
         <v>172</v>
@@ -14959,7 +14938,7 @@
         <v>173</v>
       </c>
       <c r="J230">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K230" t="s">
         <v>172</v>
@@ -14985,7 +14964,7 @@
         <v>174</v>
       </c>
       <c r="J231">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K231" t="s">
         <v>172</v>
@@ -15011,7 +14990,7 @@
         <v>171</v>
       </c>
       <c r="J232">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K232" t="s">
         <v>172</v>
@@ -15037,7 +15016,7 @@
         <v>173</v>
       </c>
       <c r="J233">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K233" t="s">
         <v>172</v>
@@ -15063,7 +15042,7 @@
         <v>174</v>
       </c>
       <c r="J234">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K234" t="s">
         <v>172</v>
@@ -15089,7 +15068,7 @@
         <v>171</v>
       </c>
       <c r="J235">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K235" t="s">
         <v>172</v>
@@ -15115,7 +15094,7 @@
         <v>173</v>
       </c>
       <c r="J236">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K236" t="s">
         <v>172</v>
@@ -15141,7 +15120,7 @@
         <v>174</v>
       </c>
       <c r="J237">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K237" t="s">
         <v>172</v>
@@ -15167,7 +15146,7 @@
         <v>171</v>
       </c>
       <c r="J238">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K238" t="s">
         <v>172</v>
@@ -15193,7 +15172,7 @@
         <v>173</v>
       </c>
       <c r="J239">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K239" t="s">
         <v>172</v>
@@ -15219,7 +15198,7 @@
         <v>174</v>
       </c>
       <c r="J240">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K240" t="s">
         <v>172</v>
@@ -15245,7 +15224,7 @@
         <v>171</v>
       </c>
       <c r="J241">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K241" t="s">
         <v>172</v>
@@ -15271,7 +15250,7 @@
         <v>173</v>
       </c>
       <c r="J242">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K242" t="s">
         <v>172</v>
@@ -15297,7 +15276,7 @@
         <v>174</v>
       </c>
       <c r="J243">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K243" t="s">
         <v>172</v>
@@ -15323,7 +15302,7 @@
         <v>171</v>
       </c>
       <c r="J244">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K244" t="s">
         <v>172</v>
@@ -15349,7 +15328,7 @@
         <v>173</v>
       </c>
       <c r="J245">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K245" t="s">
         <v>172</v>
@@ -15375,7 +15354,7 @@
         <v>174</v>
       </c>
       <c r="J246">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K246" t="s">
         <v>172</v>
@@ -15401,7 +15380,7 @@
         <v>171</v>
       </c>
       <c r="J247">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K247" t="s">
         <v>172</v>
@@ -15427,7 +15406,7 @@
         <v>173</v>
       </c>
       <c r="J248">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K248" t="s">
         <v>172</v>
@@ -15453,7 +15432,7 @@
         <v>174</v>
       </c>
       <c r="J249">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K249" t="s">
         <v>172</v>
@@ -15479,7 +15458,7 @@
         <v>171</v>
       </c>
       <c r="J250">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K250" t="s">
         <v>172</v>
@@ -15505,7 +15484,7 @@
         <v>173</v>
       </c>
       <c r="J251">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K251" t="s">
         <v>172</v>
@@ -15531,7 +15510,7 @@
         <v>174</v>
       </c>
       <c r="J252">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K252" t="s">
         <v>172</v>
@@ -15557,7 +15536,7 @@
         <v>171</v>
       </c>
       <c r="J253">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K253" t="s">
         <v>172</v>
@@ -15583,7 +15562,7 @@
         <v>173</v>
       </c>
       <c r="J254">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K254" t="s">
         <v>172</v>
@@ -15609,7 +15588,7 @@
         <v>174</v>
       </c>
       <c r="J255">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K255" t="s">
         <v>172</v>
@@ -15635,7 +15614,7 @@
         <v>171</v>
       </c>
       <c r="J256">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K256" t="s">
         <v>172</v>
@@ -15661,7 +15640,7 @@
         <v>173</v>
       </c>
       <c r="J257">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K257" t="s">
         <v>172</v>
@@ -15687,7 +15666,7 @@
         <v>174</v>
       </c>
       <c r="J258">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K258" t="s">
         <v>172</v>
@@ -15713,7 +15692,7 @@
         <v>171</v>
       </c>
       <c r="J259">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K259" t="s">
         <v>172</v>
@@ -15739,7 +15718,7 @@
         <v>173</v>
       </c>
       <c r="J260">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K260" t="s">
         <v>172</v>
@@ -15765,7 +15744,7 @@
         <v>174</v>
       </c>
       <c r="J261">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K261" t="s">
         <v>172</v>
@@ -15791,7 +15770,7 @@
         <v>171</v>
       </c>
       <c r="J262">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K262" t="s">
         <v>172</v>
@@ -15817,7 +15796,7 @@
         <v>173</v>
       </c>
       <c r="J263">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K263" t="s">
         <v>172</v>
@@ -15843,7 +15822,7 @@
         <v>174</v>
       </c>
       <c r="J264">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K264" t="s">
         <v>172</v>
@@ -15869,7 +15848,7 @@
         <v>171</v>
       </c>
       <c r="J265">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K265" t="s">
         <v>172</v>
@@ -15895,7 +15874,7 @@
         <v>173</v>
       </c>
       <c r="J266">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K266" t="s">
         <v>172</v>
@@ -15921,7 +15900,7 @@
         <v>174</v>
       </c>
       <c r="J267">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K267" t="s">
         <v>172</v>
@@ -15947,7 +15926,7 @@
         <v>171</v>
       </c>
       <c r="J268">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K268" t="s">
         <v>172</v>
@@ -15973,7 +15952,7 @@
         <v>173</v>
       </c>
       <c r="J269">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K269" t="s">
         <v>172</v>
@@ -15999,7 +15978,7 @@
         <v>174</v>
       </c>
       <c r="J270">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K270" t="s">
         <v>172</v>
@@ -16025,7 +16004,7 @@
         <v>171</v>
       </c>
       <c r="J271">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K271" t="s">
         <v>172</v>
@@ -16051,7 +16030,7 @@
         <v>173</v>
       </c>
       <c r="J272">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K272" t="s">
         <v>172</v>
@@ -16077,7 +16056,7 @@
         <v>174</v>
       </c>
       <c r="J273">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K273" t="s">
         <v>172</v>
@@ -16103,7 +16082,7 @@
         <v>171</v>
       </c>
       <c r="J274">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K274" t="s">
         <v>172</v>
@@ -16129,7 +16108,7 @@
         <v>173</v>
       </c>
       <c r="J275">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K275" t="s">
         <v>172</v>
@@ -16155,7 +16134,7 @@
         <v>174</v>
       </c>
       <c r="J276">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K276" t="s">
         <v>172</v>
@@ -16181,7 +16160,7 @@
         <v>171</v>
       </c>
       <c r="J277">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K277" t="s">
         <v>172</v>
@@ -16207,7 +16186,7 @@
         <v>173</v>
       </c>
       <c r="J278">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K278" t="s">
         <v>172</v>
@@ -16233,7 +16212,7 @@
         <v>174</v>
       </c>
       <c r="J279">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K279" t="s">
         <v>172</v>
@@ -16259,7 +16238,7 @@
         <v>171</v>
       </c>
       <c r="J280">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K280" t="s">
         <v>172</v>
@@ -16285,7 +16264,7 @@
         <v>173</v>
       </c>
       <c r="J281">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K281" t="s">
         <v>172</v>
@@ -16311,7 +16290,7 @@
         <v>174</v>
       </c>
       <c r="J282">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K282" t="s">
         <v>172</v>
@@ -16337,7 +16316,7 @@
         <v>171</v>
       </c>
       <c r="J283">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K283" t="s">
         <v>172</v>
@@ -16363,7 +16342,7 @@
         <v>173</v>
       </c>
       <c r="J284">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K284" t="s">
         <v>172</v>
@@ -16389,7 +16368,7 @@
         <v>174</v>
       </c>
       <c r="J285">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K285" t="s">
         <v>172</v>
@@ -16415,7 +16394,7 @@
         <v>171</v>
       </c>
       <c r="J286">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K286" t="s">
         <v>172</v>
@@ -16441,7 +16420,7 @@
         <v>173</v>
       </c>
       <c r="J287">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K287" t="s">
         <v>172</v>
@@ -16467,7 +16446,7 @@
         <v>174</v>
       </c>
       <c r="J288">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K288" t="s">
         <v>172</v>
@@ -16493,7 +16472,7 @@
         <v>171</v>
       </c>
       <c r="J289">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K289" t="s">
         <v>172</v>
@@ -16519,7 +16498,7 @@
         <v>173</v>
       </c>
       <c r="J290">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K290" t="s">
         <v>172</v>
@@ -16545,7 +16524,7 @@
         <v>174</v>
       </c>
       <c r="J291">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K291" t="s">
         <v>172</v>
@@ -16571,7 +16550,7 @@
         <v>171</v>
       </c>
       <c r="J292">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K292" t="s">
         <v>172</v>
@@ -16597,7 +16576,7 @@
         <v>173</v>
       </c>
       <c r="J293">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K293" t="s">
         <v>172</v>
@@ -16623,7 +16602,7 @@
         <v>174</v>
       </c>
       <c r="J294">
-        <v>0.21867712675355294</v>
+        <v>0.21780312117645417</v>
       </c>
       <c r="K294" t="s">
         <v>172</v>
@@ -16649,7 +16628,7 @@
         <v>171</v>
       </c>
       <c r="J295">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K295" t="s">
         <v>172</v>
@@ -16675,7 +16654,7 @@
         <v>173</v>
       </c>
       <c r="J296">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K296" t="s">
         <v>172</v>
@@ -16701,7 +16680,7 @@
         <v>174</v>
       </c>
       <c r="J297">
-        <v>0.14906983660935968</v>
+        <v>0.14847403644265725</v>
       </c>
       <c r="K297" t="s">
         <v>172</v>
@@ -16727,7 +16706,7 @@
         <v>171</v>
       </c>
       <c r="J298">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K298" t="s">
         <v>172</v>
@@ -16753,7 +16732,7 @@
         <v>173</v>
       </c>
       <c r="J299">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K299" t="s">
         <v>172</v>
@@ -16779,7 +16758,7 @@
         <v>174</v>
       </c>
       <c r="J300">
-        <v>5.1895746946880057E-3</v>
+        <v>5.1688330776141359E-3</v>
       </c>
       <c r="K300" t="s">
         <v>172</v>
@@ -16805,7 +16784,7 @@
         <v>171</v>
       </c>
       <c r="J301">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K301" t="s">
         <v>172</v>
@@ -16831,7 +16810,7 @@
         <v>173</v>
       </c>
       <c r="J302">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K302" t="s">
         <v>172</v>
@@ -16857,7 +16836,7 @@
         <v>174</v>
       </c>
       <c r="J303">
-        <v>2.899256796049964E-3</v>
+        <v>2.887669088424456E-3</v>
       </c>
       <c r="K303" t="s">
         <v>172</v>
@@ -16883,7 +16862,7 @@
         <v>171</v>
       </c>
       <c r="J304">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K304" t="s">
         <v>172</v>
@@ -16909,7 +16888,7 @@
         <v>173</v>
       </c>
       <c r="J305">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K305" t="s">
         <v>172</v>
@@ -16935,7 +16914,7 @@
         <v>174</v>
       </c>
       <c r="J306">
-        <v>2.2910762074896038E-2</v>
+        <v>2.28191926724335E-2</v>
       </c>
       <c r="K306" t="s">
         <v>172</v>
@@ -16961,7 +16940,7 @@
         <v>171</v>
       </c>
       <c r="J307">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K307" t="s">
         <v>172</v>
@@ -16987,7 +16966,7 @@
         <v>173</v>
       </c>
       <c r="J308">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K308" t="s">
         <v>172</v>
@@ -17013,7 +16992,7 @@
         <v>174</v>
       </c>
       <c r="J309">
-        <v>9.6035244357787132E-6</v>
+        <v>9.5651412082263667E-6</v>
       </c>
       <c r="K309" t="s">
         <v>172</v>
@@ -17039,7 +17018,7 @@
         <v>171</v>
       </c>
       <c r="J310">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K310" t="s">
         <v>172</v>
@@ -17065,7 +17044,7 @@
         <v>173</v>
       </c>
       <c r="J311">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K311" t="s">
         <v>172</v>
@@ -17091,7 +17070,7 @@
         <v>174</v>
       </c>
       <c r="J312">
-        <v>9.9677549967723002E-4</v>
+        <v>9.9279160177818612E-4</v>
       </c>
       <c r="K312" t="s">
         <v>172</v>
@@ -17117,7 +17096,7 @@
         <v>171</v>
       </c>
       <c r="J313">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K313" t="s">
         <v>172</v>
@@ -17143,7 +17122,7 @@
         <v>173</v>
       </c>
       <c r="J314">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K314" t="s">
         <v>172</v>
@@ -17169,7 +17148,7 @@
         <v>174</v>
       </c>
       <c r="J315">
-        <v>1.0056151472673039E-3</v>
+        <v>1.001595919192652E-3</v>
       </c>
       <c r="K315" t="s">
         <v>172</v>
@@ -17195,7 +17174,7 @@
         <v>171</v>
       </c>
       <c r="J316">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K316" t="s">
         <v>172</v>
@@ -17221,7 +17200,7 @@
         <v>173</v>
       </c>
       <c r="J317">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K317" t="s">
         <v>172</v>
@@ -17247,7 +17226,7 @@
         <v>174</v>
       </c>
       <c r="J318">
-        <v>3.4095783561595419E-3</v>
+        <v>3.3959510027043302E-3</v>
       </c>
       <c r="K318" t="s">
         <v>172</v>
@@ -17273,7 +17252,7 @@
         <v>171</v>
       </c>
       <c r="J319">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K319" t="s">
         <v>172</v>
@@ -17299,7 +17278,7 @@
         <v>173</v>
       </c>
       <c r="J320">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K320" t="s">
         <v>172</v>
@@ -17325,7 +17304,7 @@
         <v>174</v>
       </c>
       <c r="J321">
-        <v>3.4233766771651721E-3</v>
+        <v>3.409694174780124E-3</v>
       </c>
       <c r="K321" t="s">
         <v>172</v>
@@ -17351,7 +17330,7 @@
         <v>171</v>
       </c>
       <c r="J322">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K322" t="s">
         <v>172</v>
@@ -17377,7 +17356,7 @@
         <v>173</v>
       </c>
       <c r="J323">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K323" t="s">
         <v>172</v>
@@ -17403,7 +17382,7 @@
         <v>174</v>
       </c>
       <c r="J324">
-        <v>8.5103824099691592E-4</v>
+        <v>8.4763682366535188E-4</v>
       </c>
       <c r="K324" t="s">
         <v>172</v>
@@ -17429,7 +17408,7 @@
         <v>171</v>
       </c>
       <c r="J325">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K325" t="s">
         <v>172</v>
@@ -17455,7 +17434,7 @@
         <v>173</v>
       </c>
       <c r="J326">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K326" t="s">
         <v>172</v>
@@ -17481,7 +17460,7 @@
         <v>174</v>
       </c>
       <c r="J327">
-        <v>5.8708822210172956E-3</v>
+        <v>3.1924295877120783E-3</v>
       </c>
       <c r="K327" t="s">
         <v>172</v>
@@ -17507,7 +17486,7 @@
         <v>171</v>
       </c>
       <c r="J328">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K328" t="s">
         <v>172</v>
@@ -17533,7 +17512,7 @@
         <v>173</v>
       </c>
       <c r="J329">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K329" t="s">
         <v>172</v>
@@ -17559,7 +17538,7 @@
         <v>174</v>
       </c>
       <c r="J330">
-        <v>3.3643802398616337E-3</v>
+        <v>0.17985925165772348</v>
       </c>
       <c r="K330" t="s">
         <v>172</v>
@@ -17585,7 +17564,7 @@
         <v>171</v>
       </c>
       <c r="J331">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K331" t="s">
         <v>172</v>
@@ -17611,7 +17590,7 @@
         <v>173</v>
       </c>
       <c r="J332">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K332" t="s">
         <v>172</v>
@@ -17637,7 +17616,7 @@
         <v>174</v>
       </c>
       <c r="J333">
-        <v>3.2991996878394261E-3</v>
+        <v>3.350933533583832E-3</v>
       </c>
       <c r="K333" t="s">
         <v>172</v>
@@ -17663,7 +17642,7 @@
         <v>171</v>
       </c>
       <c r="J334">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K334" t="s">
         <v>172</v>
@@ -17689,7 +17668,7 @@
         <v>173</v>
       </c>
       <c r="J335">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K335" t="s">
         <v>172</v>
@@ -17715,7 +17694,7 @@
         <v>174</v>
       </c>
       <c r="J336">
-        <v>2.3238451331157859E-3</v>
+        <v>3.2860134942491641E-3</v>
       </c>
       <c r="K336" t="s">
         <v>172</v>
@@ -17741,7 +17720,7 @@
         <v>171</v>
       </c>
       <c r="J337">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K337" t="s">
         <v>172</v>
@@ -17767,7 +17746,7 @@
         <v>173</v>
       </c>
       <c r="J338">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K338" t="s">
         <v>172</v>
@@ -17793,7 +17772,7 @@
         <v>174</v>
       </c>
       <c r="J339">
-        <v>6.6235385850951345E-2</v>
+        <v>2.3145572225015936E-3</v>
       </c>
       <c r="K339" t="s">
         <v>172</v>
@@ -17819,7 +17798,7 @@
         <v>171</v>
       </c>
       <c r="J340">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K340" t="s">
         <v>172</v>
@@ -17845,7 +17824,7 @@
         <v>173</v>
       </c>
       <c r="J341">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K341" t="s">
         <v>172</v>
@@ -17871,7 +17850,7 @@
         <v>174</v>
       </c>
       <c r="J342">
-        <v>0.17398278573843456</v>
+        <v>6.5970657218860543E-2</v>
       </c>
       <c r="K342" t="s">
         <v>172</v>
@@ -17897,7 +17876,7 @@
         <v>171</v>
       </c>
       <c r="J343">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K343" t="s">
         <v>172</v>
@@ -17923,7 +17902,7 @@
         <v>173</v>
       </c>
       <c r="J344">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K344" t="s">
         <v>172</v>
@@ -17949,7 +17928,7 @@
         <v>174</v>
       </c>
       <c r="J345">
-        <v>2.3268397210790198E-4</v>
+        <v>2.3175398417389401E-4</v>
       </c>
       <c r="K345" t="s">
         <v>172</v>
@@ -17961,7 +17940,7 @@
         <v>686</v>
       </c>
       <c r="W345" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X345" t="s">
         <v>408</v>
@@ -17975,7 +17954,7 @@
         <v>171</v>
       </c>
       <c r="J346">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K346" t="s">
         <v>172</v>
@@ -17984,7 +17963,7 @@
         <v>108</v>
       </c>
       <c r="V346" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W346" t="s">
         <v>365</v>
@@ -18001,7 +17980,7 @@
         <v>173</v>
       </c>
       <c r="J347">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K347" t="s">
         <v>172</v>
@@ -18010,10 +17989,10 @@
         <v>108</v>
       </c>
       <c r="V347" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W347" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X347" t="s">
         <v>408</v>
@@ -18027,7 +18006,7 @@
         <v>174</v>
       </c>
       <c r="J348">
-        <v>2.8959506851114697E-3</v>
+        <v>2.88437619130234E-3</v>
       </c>
       <c r="K348" t="s">
         <v>172</v>
@@ -18036,7 +18015,7 @@
         <v>108</v>
       </c>
       <c r="V348" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="W348" t="s">
         <v>365</v>
@@ -18053,7 +18032,7 @@
         <v>171</v>
       </c>
       <c r="J349">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K349" t="s">
         <v>172</v>
@@ -18062,10 +18041,10 @@
         <v>108</v>
       </c>
       <c r="V349" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="W349" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X349" t="s">
         <v>408</v>
@@ -18079,7 +18058,7 @@
         <v>173</v>
       </c>
       <c r="J350">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K350" t="s">
         <v>172</v>
@@ -18088,10 +18067,10 @@
         <v>108</v>
       </c>
       <c r="V350" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="W350" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X350" t="s">
         <v>408</v>
@@ -18105,7 +18084,7 @@
         <v>174</v>
       </c>
       <c r="J351">
-        <v>4.0488137444905222E-3</v>
+        <v>4.0326315042817024E-3</v>
       </c>
       <c r="K351" t="s">
         <v>172</v>
@@ -18114,10 +18093,10 @@
         <v>108</v>
       </c>
       <c r="V351" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="W351" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X351" t="s">
         <v>408</v>
@@ -18131,7 +18110,7 @@
         <v>171</v>
       </c>
       <c r="J352">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K352" t="s">
         <v>172</v>
@@ -18140,10 +18119,10 @@
         <v>108</v>
       </c>
       <c r="V352" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="W352" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X352" t="s">
         <v>408</v>
@@ -18157,7 +18136,7 @@
         <v>173</v>
       </c>
       <c r="J353">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K353" t="s">
         <v>172</v>
@@ -18166,7 +18145,7 @@
         <v>108</v>
       </c>
       <c r="V353" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="W353" t="s">
         <v>365</v>
@@ -18183,7 +18162,7 @@
         <v>174</v>
       </c>
       <c r="J354">
-        <v>0.11982970995042778</v>
+        <v>0.11935077629900459</v>
       </c>
       <c r="K354" t="s">
         <v>172</v>
@@ -18192,10 +18171,10 @@
         <v>108</v>
       </c>
       <c r="V354" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="W354" t="s">
-        <v>687</v>
+        <v>394</v>
       </c>
       <c r="X354" t="s">
         <v>408</v>
@@ -18209,7 +18188,7 @@
         <v>171</v>
       </c>
       <c r="J355">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K355" t="s">
         <v>172</v>
@@ -18218,7 +18197,7 @@
         <v>108</v>
       </c>
       <c r="V355" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="W355" t="s">
         <v>365</v>
@@ -18235,7 +18214,7 @@
         <v>173</v>
       </c>
       <c r="J356">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K356" t="s">
         <v>172</v>
@@ -18244,7 +18223,7 @@
         <v>108</v>
       </c>
       <c r="V356" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="W356" t="s">
         <v>366</v>
@@ -18261,7 +18240,7 @@
         <v>174</v>
       </c>
       <c r="J357">
-        <v>1.387263424170736E-3</v>
+        <v>1.3817188297834319E-3</v>
       </c>
       <c r="K357" t="s">
         <v>172</v>
@@ -18270,7 +18249,7 @@
         <v>108</v>
       </c>
       <c r="V357" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="W357" t="s">
         <v>366</v>
@@ -18287,7 +18266,7 @@
         <v>171</v>
       </c>
       <c r="J358">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K358" t="s">
         <v>172</v>
@@ -18296,7 +18275,7 @@
         <v>108</v>
       </c>
       <c r="V358" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="W358" t="s">
         <v>366</v>
@@ -18313,7 +18292,7 @@
         <v>173</v>
       </c>
       <c r="J359">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K359" t="s">
         <v>172</v>
@@ -18322,7 +18301,7 @@
         <v>108</v>
       </c>
       <c r="V359" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="W359" t="s">
         <v>366</v>
@@ -18339,7 +18318,7 @@
         <v>174</v>
       </c>
       <c r="J360">
-        <v>1.731918287329314E-3</v>
+        <v>1.7249961813702659E-3</v>
       </c>
       <c r="K360" t="s">
         <v>172</v>
@@ -18348,7 +18327,7 @@
         <v>108</v>
       </c>
       <c r="V360" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="W360" t="s">
         <v>366</v>
@@ -18365,7 +18344,7 @@
         <v>171</v>
       </c>
       <c r="J361">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K361" t="s">
         <v>172</v>
@@ -18374,7 +18353,7 @@
         <v>108</v>
       </c>
       <c r="V361" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="W361" t="s">
         <v>366</v>
@@ -18391,7 +18370,7 @@
         <v>173</v>
       </c>
       <c r="J362">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K362" t="s">
         <v>172</v>
@@ -18400,7 +18379,7 @@
         <v>108</v>
       </c>
       <c r="V362" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="W362" t="s">
         <v>366</v>
@@ -18417,7 +18396,7 @@
         <v>174</v>
       </c>
       <c r="J363">
-        <v>3.5191369463610919E-3</v>
+        <v>3.5050717107173736E-3</v>
       </c>
       <c r="K363" t="s">
         <v>172</v>
@@ -18426,7 +18405,7 @@
         <v>108</v>
       </c>
       <c r="V363" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W363" t="s">
         <v>366</v>
@@ -18443,7 +18422,7 @@
         <v>171</v>
       </c>
       <c r="J364">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K364" t="s">
         <v>172</v>
@@ -18452,7 +18431,7 @@
         <v>108</v>
       </c>
       <c r="V364" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="W364" t="s">
         <v>366</v>
@@ -18469,7 +18448,7 @@
         <v>173</v>
       </c>
       <c r="J365">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K365" t="s">
         <v>172</v>
@@ -18478,7 +18457,7 @@
         <v>108</v>
       </c>
       <c r="V365" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="W365" t="s">
         <v>366</v>
@@ -18495,7 +18474,7 @@
         <v>174</v>
       </c>
       <c r="J366">
-        <v>7.9570859497033798E-4</v>
+        <v>7.9252831836767405E-4</v>
       </c>
       <c r="K366" t="s">
         <v>172</v>
@@ -18504,7 +18483,7 @@
         <v>108</v>
       </c>
       <c r="V366" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="W366" t="s">
         <v>366</v>
@@ -18521,7 +18500,7 @@
         <v>171</v>
       </c>
       <c r="J367">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K367" t="s">
         <v>172</v>
@@ -18530,10 +18509,10 @@
         <v>108</v>
       </c>
       <c r="V367" t="s">
+        <v>703</v>
+      </c>
+      <c r="W367" t="s">
         <v>704</v>
-      </c>
-      <c r="W367" t="s">
-        <v>397</v>
       </c>
       <c r="X367" t="s">
         <v>408</v>
@@ -18547,7 +18526,7 @@
         <v>173</v>
       </c>
       <c r="J368">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K368" t="s">
         <v>172</v>
@@ -18573,7 +18552,7 @@
         <v>174</v>
       </c>
       <c r="J369">
-        <v>1.4942537699318418E-2</v>
+        <v>1.4882815580781861E-2</v>
       </c>
       <c r="K369" t="s">
         <v>172</v>
@@ -18585,7 +18564,7 @@
         <v>705</v>
       </c>
       <c r="W369" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X369" t="s">
         <v>408</v>
@@ -18599,7 +18578,7 @@
         <v>171</v>
       </c>
       <c r="J370">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K370" t="s">
         <v>172</v>
@@ -18625,7 +18604,7 @@
         <v>173</v>
       </c>
       <c r="J371">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K371" t="s">
         <v>172</v>
@@ -18637,7 +18616,7 @@
         <v>706</v>
       </c>
       <c r="W371" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X371" t="s">
         <v>408</v>
@@ -18651,7 +18630,7 @@
         <v>174</v>
       </c>
       <c r="J372">
-        <v>8.2812063613390999E-4</v>
+        <v>8.2481081555388597E-4</v>
       </c>
       <c r="K372" t="s">
         <v>172</v>
@@ -18663,7 +18642,7 @@
         <v>707</v>
       </c>
       <c r="W372" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X372" t="s">
         <v>408</v>
@@ -18677,7 +18656,7 @@
         <v>171</v>
       </c>
       <c r="J373">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K373" t="s">
         <v>172</v>
@@ -18689,7 +18668,7 @@
         <v>708</v>
       </c>
       <c r="W373" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X373" t="s">
         <v>408</v>
@@ -18703,7 +18682,7 @@
         <v>173</v>
       </c>
       <c r="J374">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K374" t="s">
         <v>172</v>
@@ -18715,7 +18694,7 @@
         <v>709</v>
       </c>
       <c r="W374" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X374" t="s">
         <v>408</v>
@@ -18729,7 +18708,7 @@
         <v>174</v>
       </c>
       <c r="J375">
-        <v>4.9059100649283635E-2</v>
+        <v>4.8863021945436104E-2</v>
       </c>
       <c r="K375" t="s">
         <v>172</v>
@@ -18755,7 +18734,7 @@
         <v>171</v>
       </c>
       <c r="J376">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K376" t="s">
         <v>172</v>
@@ -18767,7 +18746,7 @@
         <v>710</v>
       </c>
       <c r="W376" t="s">
-        <v>397</v>
+        <v>704</v>
       </c>
       <c r="X376" t="s">
         <v>408</v>
@@ -18781,7 +18760,7 @@
         <v>173</v>
       </c>
       <c r="J377">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K377" t="s">
         <v>172</v>
@@ -18807,7 +18786,7 @@
         <v>174</v>
       </c>
       <c r="J378">
-        <v>0.10533801128641919</v>
+        <v>0.10491699784659755</v>
       </c>
       <c r="K378" t="s">
         <v>172</v>
@@ -18819,7 +18798,7 @@
         <v>711</v>
       </c>
       <c r="W378" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X378" t="s">
         <v>408</v>
@@ -18833,7 +18812,7 @@
         <v>171</v>
       </c>
       <c r="J379">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K379" t="s">
         <v>172</v>
@@ -18845,7 +18824,7 @@
         <v>712</v>
       </c>
       <c r="W379" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X379" t="s">
         <v>408</v>
@@ -18859,7 +18838,7 @@
         <v>173</v>
       </c>
       <c r="J380">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K380" t="s">
         <v>172</v>
@@ -18871,7 +18850,7 @@
         <v>713</v>
       </c>
       <c r="W380" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X380" t="s">
         <v>408</v>
@@ -18885,7 +18864,7 @@
         <v>174</v>
       </c>
       <c r="J381">
-        <v>7.0782659591376597E-4</v>
+        <v>7.0499756481383607E-4</v>
       </c>
       <c r="K381" t="s">
         <v>172</v>
@@ -18897,7 +18876,7 @@
         <v>714</v>
       </c>
       <c r="W381" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X381" t="s">
         <v>408</v>
@@ -18911,7 +18890,7 @@
         <v>171</v>
       </c>
       <c r="J382">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K382" t="s">
         <v>172</v>
@@ -18923,7 +18902,7 @@
         <v>715</v>
       </c>
       <c r="W382" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X382" t="s">
         <v>408</v>
@@ -18937,7 +18916,7 @@
         <v>173</v>
       </c>
       <c r="J383">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K383" t="s">
         <v>172</v>
@@ -18949,7 +18928,7 @@
         <v>716</v>
       </c>
       <c r="W383" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X383" t="s">
         <v>408</v>
@@ -18963,7 +18942,7 @@
         <v>174</v>
       </c>
       <c r="J384">
-        <v>9.7217415241610157E-3</v>
+        <v>9.6828858082598172E-3</v>
       </c>
       <c r="K384" t="s">
         <v>172</v>
@@ -18975,7 +18954,7 @@
         <v>717</v>
       </c>
       <c r="W384" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X384" t="s">
         <v>408</v>
@@ -18989,7 +18968,7 @@
         <v>171</v>
       </c>
       <c r="J385">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K385" t="s">
         <v>172</v>
@@ -19001,7 +18980,7 @@
         <v>718</v>
       </c>
       <c r="W385" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X385" t="s">
         <v>408</v>
@@ -19015,7 +18994,7 @@
         <v>173</v>
       </c>
       <c r="J386">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K386" t="s">
         <v>172</v>
@@ -19027,7 +19006,7 @@
         <v>719</v>
       </c>
       <c r="W386" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X386" t="s">
         <v>408</v>
@@ -19041,7 +19020,7 @@
         <v>174</v>
       </c>
       <c r="J387">
-        <v>1.4424527583307939E-3</v>
+        <v>1.436687584011064E-3</v>
       </c>
       <c r="K387" t="s">
         <v>172</v>
@@ -19053,7 +19032,7 @@
         <v>720</v>
       </c>
       <c r="W387" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X387" t="s">
         <v>408</v>
@@ -19067,7 +19046,7 @@
         <v>302</v>
       </c>
       <c r="J388">
-        <v>0.15811814990338124</v>
+        <v>0.15763211566018082</v>
       </c>
       <c r="K388" t="s">
         <v>172</v>
@@ -19079,7 +19058,7 @@
         <v>721</v>
       </c>
       <c r="W388" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X388" t="s">
         <v>408</v>
@@ -19093,7 +19072,7 @@
         <v>302</v>
       </c>
       <c r="J389">
-        <v>0.1071549514875754</v>
+        <v>0.1068236271909007</v>
       </c>
       <c r="K389" t="s">
         <v>172</v>
@@ -19105,7 +19084,7 @@
         <v>721</v>
       </c>
       <c r="W389" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X389" t="s">
         <v>408</v>
@@ -19119,7 +19098,7 @@
         <v>302</v>
       </c>
       <c r="J390">
-        <v>3.2054486488084619E-3</v>
+        <v>3.1939142416817718E-3</v>
       </c>
       <c r="K390" t="s">
         <v>172</v>
@@ -19131,7 +19110,7 @@
         <v>722</v>
       </c>
       <c r="W390" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X390" t="s">
         <v>408</v>
@@ -19145,7 +19124,7 @@
         <v>302</v>
       </c>
       <c r="J391">
-        <v>5.0326046164326102E-3</v>
+        <v>5.0261606956456002E-3</v>
       </c>
       <c r="K391" t="s">
         <v>172</v>
@@ -19157,7 +19136,7 @@
         <v>722</v>
       </c>
       <c r="W391" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X391" t="s">
         <v>408</v>
@@ -19171,7 +19150,7 @@
         <v>302</v>
       </c>
       <c r="J392">
-        <v>2.4250235956061499E-2</v>
+        <v>2.419931423840626E-2</v>
       </c>
       <c r="K392" t="s">
         <v>172</v>
@@ -19183,7 +19162,7 @@
         <v>723</v>
       </c>
       <c r="W392" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X392" t="s">
         <v>408</v>
@@ -19197,7 +19176,7 @@
         <v>302</v>
       </c>
       <c r="J393">
-        <v>2.1104771130333239E-3</v>
+        <v>2.1104557681318578E-3</v>
       </c>
       <c r="K393" t="s">
         <v>172</v>
@@ -19209,7 +19188,7 @@
         <v>723</v>
       </c>
       <c r="W393" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X393" t="s">
         <v>408</v>
@@ -19223,7 +19202,7 @@
         <v>302</v>
       </c>
       <c r="J394">
-        <v>3.7782308148764901E-3</v>
+        <v>3.7760153704319201E-3</v>
       </c>
       <c r="K394" t="s">
         <v>172</v>
@@ -19235,7 +19214,7 @@
         <v>724</v>
       </c>
       <c r="W394" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X394" t="s">
         <v>408</v>
@@ -19249,7 +19228,7 @@
         <v>302</v>
       </c>
       <c r="J395">
-        <v>7.1727579341041821E-3</v>
+        <v>7.1705228425593421E-3</v>
       </c>
       <c r="K395" t="s">
         <v>172</v>
@@ -19261,7 +19240,7 @@
         <v>725</v>
       </c>
       <c r="W395" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X395" t="s">
         <v>408</v>
@@ -19275,7 +19254,7 @@
         <v>302</v>
       </c>
       <c r="J396">
-        <v>1.7615726258763512E-2</v>
+        <v>1.7608148091533299E-2</v>
       </c>
       <c r="K396" t="s">
         <v>172</v>
@@ -19287,7 +19266,7 @@
         <v>726</v>
       </c>
       <c r="W396" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X396" t="s">
         <v>408</v>
@@ -19301,7 +19280,7 @@
         <v>302</v>
       </c>
       <c r="J397">
-        <v>7.2294941497655094E-3</v>
+        <v>7.2218853142316441E-3</v>
       </c>
       <c r="K397" t="s">
         <v>172</v>
@@ -19313,7 +19292,7 @@
         <v>726</v>
       </c>
       <c r="W397" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X397" t="s">
         <v>353</v>
@@ -19327,7 +19306,7 @@
         <v>302</v>
       </c>
       <c r="J398">
-        <v>4.7326211437985201E-4</v>
+        <v>4.7137058720672203E-4</v>
       </c>
       <c r="K398" t="s">
         <v>172</v>
@@ -19339,7 +19318,7 @@
         <v>727</v>
       </c>
       <c r="W398" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="X398" t="s">
         <v>408</v>
@@ -19353,7 +19332,7 @@
         <v>302</v>
       </c>
       <c r="J399">
-        <v>4.2765968400069456E-3</v>
+        <v>2.7871101219721058E-3</v>
       </c>
       <c r="K399" t="s">
         <v>172</v>
@@ -19365,7 +19344,7 @@
         <v>727</v>
       </c>
       <c r="W399" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X399" t="s">
         <v>353</v>
@@ -19379,7 +19358,7 @@
         <v>302</v>
       </c>
       <c r="J400">
-        <v>1.870930857384106E-3</v>
+        <v>0.10596628815665089</v>
       </c>
       <c r="K400" t="s">
         <v>172</v>
@@ -19391,7 +19370,7 @@
         <v>728</v>
       </c>
       <c r="W400" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X400" t="s">
         <v>408</v>
@@ -19405,7 +19384,7 @@
         <v>302</v>
       </c>
       <c r="J401">
-        <v>1.8346839716620799E-3</v>
+        <v>1.863453147995754E-3</v>
       </c>
       <c r="K401" t="s">
         <v>172</v>
@@ -19417,7 +19396,7 @@
         <v>729</v>
       </c>
       <c r="W401" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X401" t="s">
         <v>408</v>
@@ -19431,7 +19410,7 @@
         <v>302</v>
       </c>
       <c r="J402">
-        <v>1.2922895919477741E-3</v>
+        <v>1.8273511333023239E-3</v>
       </c>
       <c r="K402" t="s">
         <v>172</v>
@@ -19443,7 +19422,7 @@
         <v>730</v>
       </c>
       <c r="W402" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X402" t="s">
         <v>408</v>
@@ -19457,7 +19436,7 @@
         <v>302</v>
       </c>
       <c r="J403">
-        <v>4.0167184920931194E-2</v>
+        <v>1.2871245875993819E-3</v>
       </c>
       <c r="K403" t="s">
         <v>172</v>
@@ -19469,7 +19448,7 @@
         <v>731</v>
       </c>
       <c r="W403" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X403" t="s">
         <v>408</v>
@@ -19483,7 +19462,7 @@
         <v>302</v>
       </c>
       <c r="J404">
-        <v>0.10269838719513065</v>
+        <v>4.0019969406839266E-2</v>
       </c>
       <c r="K404" t="s">
         <v>172</v>
@@ -19495,7 +19474,7 @@
         <v>732</v>
       </c>
       <c r="W404" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X404" t="s">
         <v>408</v>
@@ -19509,7 +19488,7 @@
         <v>302</v>
       </c>
       <c r="J405">
-        <v>8.0998947710300207E-4</v>
+        <v>8.0947231108767807E-4</v>
       </c>
       <c r="K405" t="s">
         <v>172</v>
@@ -19521,7 +19500,7 @@
         <v>733</v>
       </c>
       <c r="W405" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X405" t="s">
         <v>408</v>
@@ -19535,7 +19514,7 @@
         <v>302</v>
       </c>
       <c r="J406">
-        <v>1.7206192839526601E-3</v>
+        <v>1.714182711365096E-3</v>
       </c>
       <c r="K406" t="s">
         <v>172</v>
@@ -19547,7 +19526,7 @@
         <v>734</v>
       </c>
       <c r="W406" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X406" t="s">
         <v>408</v>
@@ -19561,7 +19540,7 @@
         <v>302</v>
       </c>
       <c r="J407">
-        <v>2.2515441270929463E-3</v>
+        <v>2.2425451880938542E-3</v>
       </c>
       <c r="K407" t="s">
         <v>172</v>
@@ -19573,7 +19552,7 @@
         <v>735</v>
       </c>
       <c r="W407" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X407" t="s">
         <v>408</v>
@@ -19587,7 +19566,7 @@
         <v>302</v>
       </c>
       <c r="J408">
-        <v>6.6637266299858791E-2</v>
+        <v>6.6370931437802885E-2</v>
       </c>
       <c r="K408" t="s">
         <v>172</v>
@@ -19599,7 +19578,7 @@
         <v>736</v>
       </c>
       <c r="W408" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X408" t="s">
         <v>408</v>
@@ -19613,7 +19592,7 @@
         <v>302</v>
       </c>
       <c r="J409">
-        <v>7.7145678031559188E-4</v>
+        <v>7.6837343301500594E-4</v>
       </c>
       <c r="K409" t="s">
         <v>172</v>
@@ -19625,7 +19604,7 @@
         <v>737</v>
       </c>
       <c r="W409" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X409" t="s">
         <v>408</v>
@@ -19639,7 +19618,7 @@
         <v>302</v>
       </c>
       <c r="J410">
-        <v>3.8463247989379782E-3</v>
+        <v>3.842475417859302E-3</v>
       </c>
       <c r="K410" t="s">
         <v>172</v>
@@ -19651,7 +19630,7 @@
         <v>738</v>
       </c>
       <c r="W410" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X410" t="s">
         <v>408</v>
@@ -19665,7 +19644,7 @@
         <v>302</v>
       </c>
       <c r="J411">
-        <v>4.5638962741667817E-3</v>
+        <v>4.5560746007808498E-3</v>
       </c>
       <c r="K411" t="s">
         <v>172</v>
@@ -19677,7 +19656,7 @@
         <v>738</v>
       </c>
       <c r="W411" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X411" t="s">
         <v>408</v>
@@ -19691,7 +19670,7 @@
         <v>302</v>
       </c>
       <c r="J412">
-        <v>2.8350031467908259E-2</v>
+        <v>2.8348262917029146E-2</v>
       </c>
       <c r="K412" t="s">
         <v>172</v>
@@ -19700,10 +19679,10 @@
         <v>108</v>
       </c>
       <c r="V412" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="W412" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X412" t="s">
         <v>408</v>
@@ -19717,7 +19696,7 @@
         <v>302</v>
       </c>
       <c r="J413">
-        <v>8.3095407998323E-3</v>
+        <v>8.2763293473590519E-3</v>
       </c>
       <c r="K413" t="s">
         <v>172</v>
@@ -19726,10 +19705,10 @@
         <v>108</v>
       </c>
       <c r="V413" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="W413" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X413" t="s">
         <v>408</v>
@@ -19743,7 +19722,7 @@
         <v>302</v>
       </c>
       <c r="J414">
-        <v>4.6051764108655203E-4</v>
+        <v>4.5867705083991003E-4</v>
       </c>
       <c r="K414" t="s">
         <v>172</v>
@@ -19752,10 +19731,10 @@
         <v>108</v>
       </c>
       <c r="V414" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="W414" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X414" t="s">
         <v>408</v>
@@ -19769,7 +19748,7 @@
         <v>302</v>
       </c>
       <c r="J415">
-        <v>5.502277527481042E-2</v>
+        <v>5.4913735965532111E-2</v>
       </c>
       <c r="K415" t="s">
         <v>172</v>
@@ -19778,10 +19757,10 @@
         <v>108</v>
       </c>
       <c r="V415" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="W415" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X415" t="s">
         <v>408</v>
@@ -19795,7 +19774,7 @@
         <v>302</v>
       </c>
       <c r="J416">
-        <v>7.2791010093644359E-2</v>
+        <v>7.2556884644147543E-2</v>
       </c>
       <c r="K416" t="s">
         <v>172</v>
@@ -19804,10 +19783,10 @@
         <v>108</v>
       </c>
       <c r="V416" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="W416" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X416" t="s">
         <v>408</v>
@@ -19821,7 +19800,7 @@
         <v>302</v>
       </c>
       <c r="J417">
-        <v>3.9362216086090803E-4</v>
+        <v>3.9204893750206804E-4</v>
       </c>
       <c r="K417" t="s">
         <v>172</v>
@@ -19830,10 +19809,10 @@
         <v>108</v>
       </c>
       <c r="V417" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="W417" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X417" t="s">
         <v>408</v>
@@ -19847,7 +19826,7 @@
         <v>302</v>
       </c>
       <c r="J418">
-        <v>5.4062575893066298E-3</v>
+        <v>5.384649937173836E-3</v>
       </c>
       <c r="K418" t="s">
         <v>172</v>
@@ -19856,10 +19835,10 @@
         <v>108</v>
       </c>
       <c r="V418" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="W418" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X418" t="s">
         <v>408</v>
@@ -19873,7 +19852,7 @@
         <v>302</v>
       </c>
       <c r="J419">
-        <v>3.1447520629627477E-3</v>
+        <v>3.1415460512268837E-3</v>
       </c>
       <c r="K419" t="s">
         <v>172</v>
@@ -19882,10 +19861,10 @@
         <v>108</v>
       </c>
       <c r="V419" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="W419" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X419" t="s">
         <v>353</v>
@@ -19908,10 +19887,10 @@
         <v>108</v>
       </c>
       <c r="V420" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="W420" t="s">
-        <v>739</v>
+        <v>395</v>
       </c>
       <c r="X420" t="s">
         <v>408</v>
@@ -19934,10 +19913,10 @@
         <v>108</v>
       </c>
       <c r="V421" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="W421" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X421" t="s">
         <v>353</v>
@@ -19960,7 +19939,7 @@
         <v>108</v>
       </c>
       <c r="V422" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="W422" t="s">
         <v>368</v>
@@ -19986,7 +19965,7 @@
         <v>108</v>
       </c>
       <c r="V423" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="W423" t="s">
         <v>368</v>
@@ -20012,7 +19991,7 @@
         <v>108</v>
       </c>
       <c r="V424" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="W424" t="s">
         <v>368</v>
@@ -20038,7 +20017,7 @@
         <v>108</v>
       </c>
       <c r="V425" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="W425" t="s">
         <v>368</v>
@@ -20064,7 +20043,7 @@
         <v>108</v>
       </c>
       <c r="V426" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="W426" t="s">
         <v>368</v>
@@ -20090,7 +20069,7 @@
         <v>108</v>
       </c>
       <c r="V427" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="W427" t="s">
         <v>368</v>
@@ -20107,7 +20086,7 @@
         <v>302</v>
       </c>
       <c r="J428">
-        <v>0.15811814990338124</v>
+        <v>0.15763211566018082</v>
       </c>
       <c r="K428" t="s">
         <v>172</v>
@@ -20116,7 +20095,7 @@
         <v>108</v>
       </c>
       <c r="V428" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="W428" t="s">
         <v>368</v>
@@ -20133,7 +20112,7 @@
         <v>302</v>
       </c>
       <c r="J429">
-        <v>0.1071549514875754</v>
+        <v>0.1068236271909007</v>
       </c>
       <c r="K429" t="s">
         <v>172</v>
@@ -20142,7 +20121,7 @@
         <v>108</v>
       </c>
       <c r="V429" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="W429" t="s">
         <v>368</v>
@@ -20159,7 +20138,7 @@
         <v>302</v>
       </c>
       <c r="J430">
-        <v>3.2054486488084619E-3</v>
+        <v>3.1939142416817718E-3</v>
       </c>
       <c r="K430" t="s">
         <v>172</v>
@@ -20168,7 +20147,7 @@
         <v>108</v>
       </c>
       <c r="V430" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="W430" t="s">
         <v>368</v>
@@ -20185,7 +20164,7 @@
         <v>302</v>
       </c>
       <c r="J431">
-        <v>5.0326046164326102E-3</v>
+        <v>5.0261606956456002E-3</v>
       </c>
       <c r="K431" t="s">
         <v>172</v>
@@ -20194,7 +20173,7 @@
         <v>108</v>
       </c>
       <c r="V431" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="W431" t="s">
         <v>368</v>
@@ -20211,7 +20190,7 @@
         <v>302</v>
       </c>
       <c r="J432">
-        <v>2.4250235956061499E-2</v>
+        <v>2.419931423840626E-2</v>
       </c>
       <c r="K432" t="s">
         <v>172</v>
@@ -20220,7 +20199,7 @@
         <v>108</v>
       </c>
       <c r="V432" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="W432" t="s">
         <v>368</v>
@@ -20237,7 +20216,7 @@
         <v>302</v>
       </c>
       <c r="J433">
-        <v>2.1104771130333239E-3</v>
+        <v>2.1104557681318578E-3</v>
       </c>
       <c r="K433" t="s">
         <v>172</v>
@@ -20246,10 +20225,10 @@
         <v>108</v>
       </c>
       <c r="V433" t="s">
+        <v>755</v>
+      </c>
+      <c r="W433" t="s">
         <v>756</v>
-      </c>
-      <c r="W433" t="s">
-        <v>402</v>
       </c>
       <c r="X433" t="s">
         <v>408</v>
@@ -20263,7 +20242,7 @@
         <v>302</v>
       </c>
       <c r="J434">
-        <v>3.7782308148764901E-3</v>
+        <v>3.7760153704319201E-3</v>
       </c>
       <c r="K434" t="s">
         <v>172</v>
@@ -20289,7 +20268,7 @@
         <v>302</v>
       </c>
       <c r="J435">
-        <v>7.1727579341041821E-3</v>
+        <v>7.1705228425593421E-3</v>
       </c>
       <c r="K435" t="s">
         <v>172</v>
@@ -20301,7 +20280,7 @@
         <v>757</v>
       </c>
       <c r="W435" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X435" t="s">
         <v>408</v>
@@ -20315,7 +20294,7 @@
         <v>302</v>
       </c>
       <c r="J436">
-        <v>1.7615726258763512E-2</v>
+        <v>1.7608148091533299E-2</v>
       </c>
       <c r="K436" t="s">
         <v>172</v>
@@ -20341,7 +20320,7 @@
         <v>302</v>
       </c>
       <c r="J437">
-        <v>7.2294941497655094E-3</v>
+        <v>7.2218853142316441E-3</v>
       </c>
       <c r="K437" t="s">
         <v>172</v>
@@ -20353,7 +20332,7 @@
         <v>758</v>
       </c>
       <c r="W437" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X437" t="s">
         <v>408</v>
@@ -20367,7 +20346,7 @@
         <v>302</v>
       </c>
       <c r="J438">
-        <v>4.7326211437985201E-4</v>
+        <v>4.7137058720672203E-4</v>
       </c>
       <c r="K438" t="s">
         <v>172</v>
@@ -20379,7 +20358,7 @@
         <v>759</v>
       </c>
       <c r="W438" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X438" t="s">
         <v>408</v>
@@ -20393,7 +20372,7 @@
         <v>302</v>
       </c>
       <c r="J439">
-        <v>4.2765968400069456E-3</v>
+        <v>2.7871101219721058E-3</v>
       </c>
       <c r="K439" t="s">
         <v>172</v>
@@ -20405,7 +20384,7 @@
         <v>760</v>
       </c>
       <c r="W439" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X439" t="s">
         <v>408</v>
@@ -20419,7 +20398,7 @@
         <v>302</v>
       </c>
       <c r="J440">
-        <v>1.870930857384106E-3</v>
+        <v>0.10596628815665089</v>
       </c>
       <c r="K440" t="s">
         <v>172</v>
@@ -20431,7 +20410,7 @@
         <v>761</v>
       </c>
       <c r="W440" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X440" t="s">
         <v>408</v>
@@ -20445,7 +20424,7 @@
         <v>302</v>
       </c>
       <c r="J441">
-        <v>1.8346839716620799E-3</v>
+        <v>1.863453147995754E-3</v>
       </c>
       <c r="K441" t="s">
         <v>172</v>
@@ -20471,7 +20450,7 @@
         <v>302</v>
       </c>
       <c r="J442">
-        <v>1.2922895919477741E-3</v>
+        <v>1.8273511333023239E-3</v>
       </c>
       <c r="K442" t="s">
         <v>172</v>
@@ -20483,7 +20462,7 @@
         <v>762</v>
       </c>
       <c r="W442" t="s">
-        <v>402</v>
+        <v>756</v>
       </c>
       <c r="X442" t="s">
         <v>408</v>
@@ -20497,7 +20476,7 @@
         <v>302</v>
       </c>
       <c r="J443">
-        <v>4.0167184920931194E-2</v>
+        <v>1.2871245875993819E-3</v>
       </c>
       <c r="K443" t="s">
         <v>172</v>
@@ -20523,7 +20502,7 @@
         <v>302</v>
       </c>
       <c r="J444">
-        <v>0.10269838719513065</v>
+        <v>4.0019969406839266E-2</v>
       </c>
       <c r="K444" t="s">
         <v>172</v>
@@ -20549,7 +20528,7 @@
         <v>302</v>
       </c>
       <c r="J445">
-        <v>8.0998947710300207E-4</v>
+        <v>8.0947231108767807E-4</v>
       </c>
       <c r="K445" t="s">
         <v>172</v>
@@ -20575,7 +20554,7 @@
         <v>302</v>
       </c>
       <c r="J446">
-        <v>1.7206192839526601E-3</v>
+        <v>1.714182711365096E-3</v>
       </c>
       <c r="K446" t="s">
         <v>172</v>
@@ -20601,7 +20580,7 @@
         <v>302</v>
       </c>
       <c r="J447">
-        <v>2.2515441270929463E-3</v>
+        <v>2.2425451880938542E-3</v>
       </c>
       <c r="K447" t="s">
         <v>172</v>
@@ -20627,7 +20606,7 @@
         <v>302</v>
       </c>
       <c r="J448">
-        <v>6.6637266299858791E-2</v>
+        <v>6.6370931437802885E-2</v>
       </c>
       <c r="K448" t="s">
         <v>172</v>
@@ -20653,7 +20632,7 @@
         <v>302</v>
       </c>
       <c r="J449">
-        <v>7.7145678031559188E-4</v>
+        <v>7.6837343301500594E-4</v>
       </c>
       <c r="K449" t="s">
         <v>172</v>
@@ -20679,7 +20658,7 @@
         <v>302</v>
       </c>
       <c r="J450">
-        <v>3.8463247989379782E-3</v>
+        <v>3.842475417859302E-3</v>
       </c>
       <c r="K450" t="s">
         <v>172</v>
@@ -20705,7 +20684,7 @@
         <v>302</v>
       </c>
       <c r="J451">
-        <v>4.5638962741667817E-3</v>
+        <v>4.5560746007808498E-3</v>
       </c>
       <c r="K451" t="s">
         <v>172</v>
@@ -20731,7 +20710,7 @@
         <v>302</v>
       </c>
       <c r="J452">
-        <v>2.8350031467908259E-2</v>
+        <v>2.8348262917029146E-2</v>
       </c>
       <c r="K452" t="s">
         <v>172</v>
@@ -20757,7 +20736,7 @@
         <v>302</v>
       </c>
       <c r="J453">
-        <v>8.3095407998323E-3</v>
+        <v>8.2763293473590519E-3</v>
       </c>
       <c r="K453" t="s">
         <v>172</v>
@@ -20783,7 +20762,7 @@
         <v>302</v>
       </c>
       <c r="J454">
-        <v>4.6051764108655203E-4</v>
+        <v>4.5867705083991003E-4</v>
       </c>
       <c r="K454" t="s">
         <v>172</v>
@@ -20809,7 +20788,7 @@
         <v>302</v>
       </c>
       <c r="J455">
-        <v>5.502277527481042E-2</v>
+        <v>5.4913735965532111E-2</v>
       </c>
       <c r="K455" t="s">
         <v>172</v>
@@ -20821,7 +20800,7 @@
         <v>773</v>
       </c>
       <c r="W455" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X455" t="s">
         <v>408</v>
@@ -20835,7 +20814,7 @@
         <v>302</v>
       </c>
       <c r="J456">
-        <v>7.2791010093644359E-2</v>
+        <v>7.2556884644147543E-2</v>
       </c>
       <c r="K456" t="s">
         <v>172</v>
@@ -20861,7 +20840,7 @@
         <v>302</v>
       </c>
       <c r="J457">
-        <v>3.9362216086090803E-4</v>
+        <v>3.9204893750206804E-4</v>
       </c>
       <c r="K457" t="s">
         <v>172</v>
@@ -20873,7 +20852,7 @@
         <v>774</v>
       </c>
       <c r="W457" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X457" t="s">
         <v>408</v>
@@ -20887,7 +20866,7 @@
         <v>302</v>
       </c>
       <c r="J458">
-        <v>5.4062575893066298E-3</v>
+        <v>5.384649937173836E-3</v>
       </c>
       <c r="K458" t="s">
         <v>172</v>
@@ -20913,7 +20892,7 @@
         <v>302</v>
       </c>
       <c r="J459">
-        <v>3.1447520629627477E-3</v>
+        <v>3.1415460512268837E-3</v>
       </c>
       <c r="K459" t="s">
         <v>172</v>
@@ -20925,7 +20904,7 @@
         <v>775</v>
       </c>
       <c r="W459" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X459" t="s">
         <v>408</v>
@@ -20951,7 +20930,7 @@
         <v>776</v>
       </c>
       <c r="W460" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X460" t="s">
         <v>408</v>
@@ -20977,7 +20956,7 @@
         <v>777</v>
       </c>
       <c r="W461" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X461" t="s">
         <v>408</v>
@@ -21003,7 +20982,7 @@
         <v>778</v>
       </c>
       <c r="W462" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X462" t="s">
         <v>408</v>
@@ -21055,7 +21034,7 @@
         <v>779</v>
       </c>
       <c r="W464" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="X464" t="s">
         <v>408</v>
@@ -21147,7 +21126,7 @@
         <v>302</v>
       </c>
       <c r="J468">
-        <v>0.15811814990338124</v>
+        <v>0.15763211566018082</v>
       </c>
       <c r="K468" t="s">
         <v>172</v>
@@ -21173,7 +21152,7 @@
         <v>302</v>
       </c>
       <c r="J469">
-        <v>0.1071549514875754</v>
+        <v>0.1068236271909007</v>
       </c>
       <c r="K469" t="s">
         <v>172</v>
@@ -21199,7 +21178,7 @@
         <v>302</v>
       </c>
       <c r="J470">
-        <v>3.2054486488084619E-3</v>
+        <v>3.1939142416817718E-3</v>
       </c>
       <c r="K470" t="s">
         <v>172</v>
@@ -21225,7 +21204,7 @@
         <v>302</v>
       </c>
       <c r="J471">
-        <v>5.0326046164326102E-3</v>
+        <v>5.0261606956456002E-3</v>
       </c>
       <c r="K471" t="s">
         <v>172</v>
@@ -21251,7 +21230,7 @@
         <v>302</v>
       </c>
       <c r="J472">
-        <v>2.4250235956061499E-2</v>
+        <v>2.419931423840626E-2</v>
       </c>
       <c r="K472" t="s">
         <v>172</v>
@@ -21277,7 +21256,7 @@
         <v>302</v>
       </c>
       <c r="J473">
-        <v>2.1104771130333239E-3</v>
+        <v>2.1104557681318578E-3</v>
       </c>
       <c r="K473" t="s">
         <v>172</v>
@@ -21303,7 +21282,7 @@
         <v>302</v>
       </c>
       <c r="J474">
-        <v>3.7782308148764901E-3</v>
+        <v>3.7760153704319201E-3</v>
       </c>
       <c r="K474" t="s">
         <v>172</v>
@@ -21329,7 +21308,7 @@
         <v>302</v>
       </c>
       <c r="J475">
-        <v>7.1727579341041821E-3</v>
+        <v>7.1705228425593421E-3</v>
       </c>
       <c r="K475" t="s">
         <v>172</v>
@@ -21355,7 +21334,7 @@
         <v>302</v>
       </c>
       <c r="J476">
-        <v>1.7615726258763512E-2</v>
+        <v>1.7608148091533299E-2</v>
       </c>
       <c r="K476" t="s">
         <v>172</v>
@@ -21381,7 +21360,7 @@
         <v>302</v>
       </c>
       <c r="J477">
-        <v>7.2294941497655094E-3</v>
+        <v>7.2218853142316441E-3</v>
       </c>
       <c r="K477" t="s">
         <v>172</v>
@@ -21407,7 +21386,7 @@
         <v>302</v>
       </c>
       <c r="J478">
-        <v>4.7326211437985201E-4</v>
+        <v>4.7137058720672203E-4</v>
       </c>
       <c r="K478" t="s">
         <v>172</v>
@@ -21433,7 +21412,7 @@
         <v>302</v>
       </c>
       <c r="J479">
-        <v>4.2765968400069456E-3</v>
+        <v>2.7871101219721058E-3</v>
       </c>
       <c r="K479" t="s">
         <v>172</v>
@@ -21459,7 +21438,7 @@
         <v>302</v>
       </c>
       <c r="J480">
-        <v>1.870930857384106E-3</v>
+        <v>0.10596628815665089</v>
       </c>
       <c r="K480" t="s">
         <v>172</v>
@@ -21485,7 +21464,7 @@
         <v>302</v>
       </c>
       <c r="J481">
-        <v>1.8346839716620799E-3</v>
+        <v>1.863453147995754E-3</v>
       </c>
       <c r="K481" t="s">
         <v>172</v>
@@ -21511,7 +21490,7 @@
         <v>302</v>
       </c>
       <c r="J482">
-        <v>1.2922895919477741E-3</v>
+        <v>1.8273511333023239E-3</v>
       </c>
       <c r="K482" t="s">
         <v>172</v>
@@ -21537,7 +21516,7 @@
         <v>302</v>
       </c>
       <c r="J483">
-        <v>4.0167184920931194E-2</v>
+        <v>1.2871245875993819E-3</v>
       </c>
       <c r="K483" t="s">
         <v>172</v>
@@ -21563,7 +21542,7 @@
         <v>302</v>
       </c>
       <c r="J484">
-        <v>0.10269838719513065</v>
+        <v>4.0019969406839266E-2</v>
       </c>
       <c r="K484" t="s">
         <v>172</v>
@@ -21589,7 +21568,7 @@
         <v>302</v>
       </c>
       <c r="J485">
-        <v>8.0998947710300207E-4</v>
+        <v>8.0947231108767807E-4</v>
       </c>
       <c r="K485" t="s">
         <v>172</v>
@@ -21615,7 +21594,7 @@
         <v>302</v>
       </c>
       <c r="J486">
-        <v>1.7206192839526601E-3</v>
+        <v>1.714182711365096E-3</v>
       </c>
       <c r="K486" t="s">
         <v>172</v>
@@ -21641,7 +21620,7 @@
         <v>302</v>
       </c>
       <c r="J487">
-        <v>2.2515441270929463E-3</v>
+        <v>2.2425451880938542E-3</v>
       </c>
       <c r="K487" t="s">
         <v>172</v>
@@ -21667,7 +21646,7 @@
         <v>302</v>
       </c>
       <c r="J488">
-        <v>6.6637266299858791E-2</v>
+        <v>6.6370931437802885E-2</v>
       </c>
       <c r="K488" t="s">
         <v>172</v>
@@ -21693,7 +21672,7 @@
         <v>302</v>
       </c>
       <c r="J489">
-        <v>7.7145678031559188E-4</v>
+        <v>7.6837343301500594E-4</v>
       </c>
       <c r="K489" t="s">
         <v>172</v>
@@ -21719,7 +21698,7 @@
         <v>302</v>
       </c>
       <c r="J490">
-        <v>3.8463247989379782E-3</v>
+        <v>3.842475417859302E-3</v>
       </c>
       <c r="K490" t="s">
         <v>172</v>
@@ -21745,7 +21724,7 @@
         <v>302</v>
       </c>
       <c r="J491">
-        <v>4.5638962741667817E-3</v>
+        <v>4.5560746007808498E-3</v>
       </c>
       <c r="K491" t="s">
         <v>172</v>
@@ -21771,7 +21750,7 @@
         <v>302</v>
       </c>
       <c r="J492">
-        <v>2.8350031467908259E-2</v>
+        <v>2.8348262917029146E-2</v>
       </c>
       <c r="K492" t="s">
         <v>172</v>
@@ -21797,7 +21776,7 @@
         <v>302</v>
       </c>
       <c r="J493">
-        <v>8.3095407998323E-3</v>
+        <v>8.2763293473590519E-3</v>
       </c>
       <c r="K493" t="s">
         <v>172</v>
@@ -21823,7 +21802,7 @@
         <v>302</v>
       </c>
       <c r="J494">
-        <v>4.6051764108655203E-4</v>
+        <v>4.5867705083991003E-4</v>
       </c>
       <c r="K494" t="s">
         <v>172</v>
@@ -21849,7 +21828,7 @@
         <v>302</v>
       </c>
       <c r="J495">
-        <v>5.502277527481042E-2</v>
+        <v>5.4913735965532111E-2</v>
       </c>
       <c r="K495" t="s">
         <v>172</v>
@@ -21875,7 +21854,7 @@
         <v>302</v>
       </c>
       <c r="J496">
-        <v>7.2791010093644359E-2</v>
+        <v>7.2556884644147543E-2</v>
       </c>
       <c r="K496" t="s">
         <v>172</v>
@@ -21901,7 +21880,7 @@
         <v>302</v>
       </c>
       <c r="J497">
-        <v>3.9362216086090803E-4</v>
+        <v>3.9204893750206804E-4</v>
       </c>
       <c r="K497" t="s">
         <v>172</v>
@@ -21927,7 +21906,7 @@
         <v>302</v>
       </c>
       <c r="J498">
-        <v>5.4062575893066298E-3</v>
+        <v>5.384649937173836E-3</v>
       </c>
       <c r="K498" t="s">
         <v>172</v>
@@ -21953,7 +21932,7 @@
         <v>302</v>
       </c>
       <c r="J499">
-        <v>3.1447520629627477E-3</v>
+        <v>3.1415460512268837E-3</v>
       </c>
       <c r="K499" t="s">
         <v>172</v>
@@ -22187,7 +22166,7 @@
         <v>302</v>
       </c>
       <c r="J508">
-        <v>0.15811814990338124</v>
+        <v>0.15763211566018082</v>
       </c>
       <c r="K508" t="s">
         <v>172</v>
@@ -22213,7 +22192,7 @@
         <v>302</v>
       </c>
       <c r="J509">
-        <v>0.1071549514875754</v>
+        <v>0.1068236271909007</v>
       </c>
       <c r="K509" t="s">
         <v>172</v>
@@ -22239,7 +22218,7 @@
         <v>302</v>
       </c>
       <c r="J510">
-        <v>3.2054486488084619E-3</v>
+        <v>3.1939142416817718E-3</v>
       </c>
       <c r="K510" t="s">
         <v>172</v>
@@ -22265,7 +22244,7 @@
         <v>302</v>
       </c>
       <c r="J511">
-        <v>5.0326046164326102E-3</v>
+        <v>5.0261606956456002E-3</v>
       </c>
       <c r="K511" t="s">
         <v>172</v>
@@ -22291,7 +22270,7 @@
         <v>302</v>
       </c>
       <c r="J512">
-        <v>2.4250235956061499E-2</v>
+        <v>2.419931423840626E-2</v>
       </c>
       <c r="K512" t="s">
         <v>172</v>
@@ -22317,7 +22296,7 @@
         <v>302</v>
       </c>
       <c r="J513">
-        <v>2.1104771130333239E-3</v>
+        <v>2.1104557681318578E-3</v>
       </c>
       <c r="K513" t="s">
         <v>172</v>
@@ -22343,7 +22322,7 @@
         <v>302</v>
       </c>
       <c r="J514">
-        <v>3.7782308148764901E-3</v>
+        <v>3.7760153704319201E-3</v>
       </c>
       <c r="K514" t="s">
         <v>172</v>
@@ -22369,7 +22348,7 @@
         <v>302</v>
       </c>
       <c r="J515">
-        <v>7.1727579341041821E-3</v>
+        <v>7.1705228425593421E-3</v>
       </c>
       <c r="K515" t="s">
         <v>172</v>
@@ -22395,7 +22374,7 @@
         <v>302</v>
       </c>
       <c r="J516">
-        <v>1.7615726258763512E-2</v>
+        <v>1.7608148091533299E-2</v>
       </c>
       <c r="K516" t="s">
         <v>172</v>
@@ -22421,7 +22400,7 @@
         <v>302</v>
       </c>
       <c r="J517">
-        <v>7.2294941497655094E-3</v>
+        <v>7.2218853142316441E-3</v>
       </c>
       <c r="K517" t="s">
         <v>172</v>
@@ -22447,7 +22426,7 @@
         <v>302</v>
       </c>
       <c r="J518">
-        <v>4.7326211437985201E-4</v>
+        <v>4.7137058720672203E-4</v>
       </c>
       <c r="K518" t="s">
         <v>172</v>
@@ -22473,7 +22452,7 @@
         <v>302</v>
       </c>
       <c r="J519">
-        <v>4.2765968400069456E-3</v>
+        <v>2.7871101219721058E-3</v>
       </c>
       <c r="K519" t="s">
         <v>172</v>
@@ -22499,7 +22478,7 @@
         <v>302</v>
       </c>
       <c r="J520">
-        <v>1.870930857384106E-3</v>
+        <v>0.10596628815665089</v>
       </c>
       <c r="K520" t="s">
         <v>172</v>
@@ -22525,7 +22504,7 @@
         <v>302</v>
       </c>
       <c r="J521">
-        <v>1.8346839716620799E-3</v>
+        <v>1.863453147995754E-3</v>
       </c>
       <c r="K521" t="s">
         <v>172</v>
@@ -22551,7 +22530,7 @@
         <v>302</v>
       </c>
       <c r="J522">
-        <v>1.2922895919477741E-3</v>
+        <v>1.8273511333023239E-3</v>
       </c>
       <c r="K522" t="s">
         <v>172</v>
@@ -22577,7 +22556,7 @@
         <v>302</v>
       </c>
       <c r="J523">
-        <v>4.0167184920931194E-2</v>
+        <v>1.2871245875993819E-3</v>
       </c>
       <c r="K523" t="s">
         <v>172</v>
@@ -22603,7 +22582,7 @@
         <v>302</v>
       </c>
       <c r="J524">
-        <v>0.10269838719513065</v>
+        <v>4.0019969406839266E-2</v>
       </c>
       <c r="K524" t="s">
         <v>172</v>
@@ -22629,7 +22608,7 @@
         <v>302</v>
       </c>
       <c r="J525">
-        <v>8.0998947710300207E-4</v>
+        <v>8.0947231108767807E-4</v>
       </c>
       <c r="K525" t="s">
         <v>172</v>
@@ -22655,7 +22634,7 @@
         <v>302</v>
       </c>
       <c r="J526">
-        <v>1.7206192839526601E-3</v>
+        <v>1.714182711365096E-3</v>
       </c>
       <c r="K526" t="s">
         <v>172</v>
@@ -22681,7 +22660,7 @@
         <v>302</v>
       </c>
       <c r="J527">
-        <v>2.2515441270929463E-3</v>
+        <v>2.2425451880938542E-3</v>
       </c>
       <c r="K527" t="s">
         <v>172</v>
@@ -22707,7 +22686,7 @@
         <v>302</v>
       </c>
       <c r="J528">
-        <v>6.6637266299858791E-2</v>
+        <v>6.6370931437802885E-2</v>
       </c>
       <c r="K528" t="s">
         <v>172</v>
@@ -22733,7 +22712,7 @@
         <v>302</v>
       </c>
       <c r="J529">
-        <v>7.7145678031559188E-4</v>
+        <v>7.6837343301500594E-4</v>
       </c>
       <c r="K529" t="s">
         <v>172</v>
@@ -22759,7 +22738,7 @@
         <v>302</v>
       </c>
       <c r="J530">
-        <v>3.8463247989379782E-3</v>
+        <v>3.842475417859302E-3</v>
       </c>
       <c r="K530" t="s">
         <v>172</v>
@@ -22785,7 +22764,7 @@
         <v>302</v>
       </c>
       <c r="J531">
-        <v>4.5638962741667817E-3</v>
+        <v>4.5560746007808498E-3</v>
       </c>
       <c r="K531" t="s">
         <v>172</v>
@@ -22811,7 +22790,7 @@
         <v>302</v>
       </c>
       <c r="J532">
-        <v>2.8350031467908259E-2</v>
+        <v>2.8348262917029146E-2</v>
       </c>
       <c r="K532" t="s">
         <v>172</v>
@@ -22837,7 +22816,7 @@
         <v>302</v>
       </c>
       <c r="J533">
-        <v>8.3095407998323E-3</v>
+        <v>8.2763293473590519E-3</v>
       </c>
       <c r="K533" t="s">
         <v>172</v>
@@ -22863,7 +22842,7 @@
         <v>302</v>
       </c>
       <c r="J534">
-        <v>4.6051764108655203E-4</v>
+        <v>4.5867705083991003E-4</v>
       </c>
       <c r="K534" t="s">
         <v>172</v>
@@ -22889,7 +22868,7 @@
         <v>302</v>
       </c>
       <c r="J535">
-        <v>5.502277527481042E-2</v>
+        <v>5.4913735965532111E-2</v>
       </c>
       <c r="K535" t="s">
         <v>172</v>
@@ -22915,7 +22894,7 @@
         <v>302</v>
       </c>
       <c r="J536">
-        <v>7.2791010093644359E-2</v>
+        <v>7.2556884644147543E-2</v>
       </c>
       <c r="K536" t="s">
         <v>172</v>
@@ -22941,7 +22920,7 @@
         <v>302</v>
       </c>
       <c r="J537">
-        <v>3.9362216086090803E-4</v>
+        <v>3.9204893750206804E-4</v>
       </c>
       <c r="K537" t="s">
         <v>172</v>
@@ -22967,7 +22946,7 @@
         <v>302</v>
       </c>
       <c r="J538">
-        <v>5.4062575893066298E-3</v>
+        <v>5.384649937173836E-3</v>
       </c>
       <c r="K538" t="s">
         <v>172</v>
@@ -22993,7 +22972,7 @@
         <v>302</v>
       </c>
       <c r="J539">
-        <v>3.1447520629627477E-3</v>
+        <v>3.1415460512268837E-3</v>
       </c>
       <c r="K539" t="s">
         <v>172</v>
@@ -23227,7 +23206,7 @@
         <v>336</v>
       </c>
       <c r="J548">
-        <v>0.4328576065151728</v>
+        <v>0.42816827546224839</v>
       </c>
       <c r="K548" t="s">
         <v>172</v>
@@ -23253,7 +23232,7 @@
         <v>337</v>
       </c>
       <c r="J549">
-        <v>0.36585632861159129</v>
+        <v>0.36297321505293417</v>
       </c>
       <c r="K549" t="s">
         <v>172</v>
@@ -23279,7 +23258,7 @@
         <v>336</v>
       </c>
       <c r="J550">
-        <v>0.28301057778288319</v>
+        <v>0.29056136144006739</v>
       </c>
       <c r="K550" t="s">
         <v>172</v>
@@ -23305,7 +23284,7 @@
         <v>337</v>
       </c>
       <c r="J551">
-        <v>0.20433035907303429</v>
+        <v>0.2098457228954623</v>
       </c>
       <c r="K551" t="s">
         <v>172</v>
@@ -23331,7 +23310,7 @@
         <v>337</v>
       </c>
       <c r="J552">
-        <v>2.2069161372877798E-2</v>
+        <v>2.1965897633891299E-2</v>
       </c>
       <c r="K552" t="s">
         <v>172</v>
@@ -23357,7 +23336,7 @@
         <v>336</v>
       </c>
       <c r="J553">
-        <v>4.8326421217164996E-3</v>
+        <v>4.7802880486265999E-3</v>
       </c>
       <c r="K553" t="s">
         <v>172</v>
@@ -23383,7 +23362,7 @@
         <v>337</v>
       </c>
       <c r="J554">
-        <v>3.0539181951202199E-2</v>
+        <v>3.0383209888983999E-2</v>
       </c>
       <c r="K554" t="s">
         <v>172</v>
@@ -23409,7 +23388,7 @@
         <v>336</v>
       </c>
       <c r="J555">
-        <v>1.3142868306245E-3</v>
+        <v>1.3000486008821E-3</v>
       </c>
       <c r="K555" t="s">
         <v>172</v>
@@ -23435,7 +23414,7 @@
         <v>337</v>
       </c>
       <c r="J556">
-        <v>8.9395510274919998E-4</v>
+        <v>8.8621597176480001E-4</v>
       </c>
       <c r="K556" t="s">
         <v>172</v>
@@ -23461,7 +23440,7 @@
         <v>336</v>
       </c>
       <c r="J557">
-        <v>2.1972175195650399E-2</v>
+        <v>2.1734141251243701E-2</v>
       </c>
       <c r="K557" t="s">
         <v>172</v>
@@ -23487,7 +23466,7 @@
         <v>337</v>
       </c>
       <c r="J558">
-        <v>1.9318277885614701E-2</v>
+        <v>1.91684329605111E-2</v>
       </c>
       <c r="K558" t="s">
         <v>172</v>
@@ -23513,7 +23492,7 @@
         <v>336</v>
       </c>
       <c r="J559">
-        <v>4.24857514906982E-2</v>
+        <v>4.2025485225826199E-2</v>
       </c>
       <c r="K559" t="s">
         <v>172</v>
@@ -23539,7 +23518,7 @@
         <v>337</v>
       </c>
       <c r="J560">
-        <v>5.8282624625514999E-2</v>
+        <v>5.7894955632102799E-2</v>
       </c>
       <c r="K560" t="s">
         <v>172</v>
@@ -23565,7 +23544,7 @@
         <v>336</v>
       </c>
       <c r="J561">
-        <v>4.3020460616542897E-2</v>
+        <v>4.2554401619672298E-2</v>
       </c>
       <c r="K561" t="s">
         <v>172</v>
@@ -23591,7 +23570,7 @@
         <v>337</v>
       </c>
       <c r="J562">
-        <v>3.1910181047547302E-2</v>
+        <v>3.16444644377505E-2</v>
       </c>
       <c r="K562" t="s">
         <v>172</v>
@@ -23617,7 +23596,7 @@
         <v>336</v>
       </c>
       <c r="J563">
-        <v>0.1262512893087728</v>
+        <v>0.1248835552490813</v>
       </c>
       <c r="K563" t="s">
         <v>172</v>
@@ -23643,7 +23622,7 @@
         <v>337</v>
       </c>
       <c r="J564">
-        <v>0.111657287747638</v>
+        <v>0.11079321875640109</v>
       </c>
       <c r="K564" t="s">
         <v>172</v>
@@ -23669,7 +23648,7 @@
         <v>336</v>
       </c>
       <c r="J565">
-        <v>2.31303141097218E-2</v>
+        <v>2.2879733552545301E-2</v>
       </c>
       <c r="K565" t="s">
         <v>172</v>
@@ -23695,7 +23674,7 @@
         <v>337</v>
       </c>
       <c r="J566">
-        <v>1.7474770241185902E-2</v>
+        <v>1.73304175466177E-2</v>
       </c>
       <c r="K566" t="s">
         <v>172</v>
@@ -23721,7 +23700,7 @@
         <v>337</v>
       </c>
       <c r="J567">
-        <v>0.1146122207950519</v>
+        <v>0.1140759391370007</v>
       </c>
       <c r="K567" t="s">
         <v>172</v>
@@ -23747,7 +23726,7 @@
         <v>336</v>
       </c>
       <c r="J568">
-        <v>1.1248960282163999E-3</v>
+        <v>1.1127095498064E-3</v>
       </c>
       <c r="K568" t="s">
         <v>172</v>
@@ -23773,7 +23752,7 @@
         <v>337</v>
       </c>
       <c r="J569">
-        <v>3.0556515459917999E-3</v>
+        <v>3.0383100865789001E-3</v>
       </c>
       <c r="K569" t="s">
         <v>172</v>
@@ -29119,7 +29098,7 @@
         <v>1175</v>
       </c>
       <c r="W950" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X950" t="s">
         <v>408</v>
@@ -29133,7 +29112,7 @@
         <v>1176</v>
       </c>
       <c r="W951" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X951" t="s">
         <v>408</v>
@@ -29147,7 +29126,7 @@
         <v>1177</v>
       </c>
       <c r="W952" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X952" t="s">
         <v>408</v>
@@ -29161,7 +29140,7 @@
         <v>1178</v>
       </c>
       <c r="W953" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X953" t="s">
         <v>408</v>
@@ -29175,7 +29154,7 @@
         <v>1179</v>
       </c>
       <c r="W954" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X954" t="s">
         <v>408</v>
@@ -29189,7 +29168,7 @@
         <v>1180</v>
       </c>
       <c r="W955" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X955" t="s">
         <v>408</v>
@@ -29203,7 +29182,7 @@
         <v>1181</v>
       </c>
       <c r="W956" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X956" t="s">
         <v>408</v>
@@ -29217,7 +29196,7 @@
         <v>1182</v>
       </c>
       <c r="W957" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X957" t="s">
         <v>408</v>
@@ -29231,7 +29210,7 @@
         <v>1183</v>
       </c>
       <c r="W958" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X958" t="s">
         <v>408</v>
@@ -29245,7 +29224,7 @@
         <v>1184</v>
       </c>
       <c r="W959" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X959" t="s">
         <v>408</v>
@@ -29259,7 +29238,7 @@
         <v>1185</v>
       </c>
       <c r="W960" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X960" t="s">
         <v>408</v>
@@ -29287,7 +29266,7 @@
         <v>1187</v>
       </c>
       <c r="W962" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X962" t="s">
         <v>408</v>
@@ -29315,7 +29294,7 @@
         <v>1188</v>
       </c>
       <c r="W964" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X964" t="s">
         <v>408</v>
@@ -29385,7 +29364,7 @@
         <v>1191</v>
       </c>
       <c r="W969" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X969" t="s">
         <v>353</v>
@@ -29413,7 +29392,7 @@
         <v>1192</v>
       </c>
       <c r="W971" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X971" t="s">
         <v>353</v>
@@ -29427,7 +29406,7 @@
         <v>1193</v>
       </c>
       <c r="W972" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X972" t="s">
         <v>408</v>
@@ -29441,7 +29420,7 @@
         <v>1194</v>
       </c>
       <c r="W973" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X973" t="s">
         <v>408</v>
@@ -29455,7 +29434,7 @@
         <v>1195</v>
       </c>
       <c r="W974" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X974" t="s">
         <v>408</v>
@@ -29469,7 +29448,7 @@
         <v>1196</v>
       </c>
       <c r="W975" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X975" t="s">
         <v>408</v>
@@ -29483,7 +29462,7 @@
         <v>1197</v>
       </c>
       <c r="W976" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X976" t="s">
         <v>408</v>
@@ -29497,7 +29476,7 @@
         <v>1198</v>
       </c>
       <c r="W977" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X977" t="s">
         <v>408</v>
@@ -29511,7 +29490,7 @@
         <v>1199</v>
       </c>
       <c r="W978" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X978" t="s">
         <v>408</v>
@@ -29525,7 +29504,7 @@
         <v>1200</v>
       </c>
       <c r="W979" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X979" t="s">
         <v>408</v>
@@ -29539,7 +29518,7 @@
         <v>1201</v>
       </c>
       <c r="W980" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X980" t="s">
         <v>408</v>
@@ -29553,7 +29532,7 @@
         <v>1202</v>
       </c>
       <c r="W981" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X981" t="s">
         <v>408</v>
@@ -29567,7 +29546,7 @@
         <v>1203</v>
       </c>
       <c r="W982" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X982" t="s">
         <v>408</v>
@@ -29595,7 +29574,7 @@
         <v>1205</v>
       </c>
       <c r="W984" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X984" t="s">
         <v>408</v>
@@ -29623,7 +29602,7 @@
         <v>1206</v>
       </c>
       <c r="W986" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X986" t="s">
         <v>408</v>
@@ -29693,7 +29672,7 @@
         <v>1209</v>
       </c>
       <c r="W991" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X991" t="s">
         <v>353</v>
@@ -29721,7 +29700,7 @@
         <v>1210</v>
       </c>
       <c r="W993" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X993" t="s">
         <v>353</v>
@@ -30995,7 +30974,7 @@
         <v>1263</v>
       </c>
       <c r="W1084" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X1084" t="s">
         <v>408</v>
@@ -31009,7 +30988,7 @@
         <v>1263</v>
       </c>
       <c r="W1085" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X1085" t="s">
         <v>353</v>
@@ -31023,7 +31002,7 @@
         <v>1264</v>
       </c>
       <c r="W1086" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X1086" t="s">
         <v>408</v>
@@ -31037,7 +31016,7 @@
         <v>1264</v>
       </c>
       <c r="W1087" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="X1087" t="s">
         <v>353</v>
@@ -31051,7 +31030,7 @@
         <v>1265</v>
       </c>
       <c r="W1088" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X1088" t="s">
         <v>408</v>
@@ -31065,7 +31044,7 @@
         <v>1265</v>
       </c>
       <c r="W1089" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X1089" t="s">
         <v>353</v>
@@ -31079,7 +31058,7 @@
         <v>1266</v>
       </c>
       <c r="W1090" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X1090" t="s">
         <v>408</v>
@@ -31093,7 +31072,7 @@
         <v>1266</v>
       </c>
       <c r="W1091" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="X1091" t="s">
         <v>353</v>
@@ -32451,7 +32430,7 @@
         <v>1315</v>
       </c>
       <c r="W1188" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X1188" t="s">
         <v>408</v>
@@ -32465,7 +32444,7 @@
         <v>1315</v>
       </c>
       <c r="W1189" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X1189" t="s">
         <v>353</v>
@@ -32479,7 +32458,7 @@
         <v>1316</v>
       </c>
       <c r="W1190" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X1190" t="s">
         <v>408</v>
@@ -32493,7 +32472,7 @@
         <v>1316</v>
       </c>
       <c r="W1191" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="X1191" t="s">
         <v>353</v>
@@ -32507,7 +32486,7 @@
         <v>1317</v>
       </c>
       <c r="W1192" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X1192" t="s">
         <v>408</v>
@@ -32521,7 +32500,7 @@
         <v>1317</v>
       </c>
       <c r="W1193" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X1193" t="s">
         <v>353</v>
@@ -32535,7 +32514,7 @@
         <v>1318</v>
       </c>
       <c r="W1194" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X1194" t="s">
         <v>408</v>
@@ -32549,7 +32528,7 @@
         <v>1318</v>
       </c>
       <c r="W1195" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="X1195" t="s">
         <v>353</v>
@@ -32617,7 +32596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D570836-1A35-4C37-9D75-F7BA4F2FA202}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6221AA-0D32-41F9-A1EC-7F9A3B86FEB6}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -45019,7 +44998,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{368B41F9-ABBB-48EE-AFF5-38B74EEC8137}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923DFD3A-1386-4CE4-B7C7-F283DAFB6830}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA708CB-5F94-4103-B14E-2BE39A355342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E0E53-7B3D-48CF-99BA-EA039CCA0C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6205,7 +6205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A66F8A8-0780-436A-8BC5-057B5F1E02C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD2C11B-2C48-4F2B-94D1-4E4EE040316A}">
   <dimension ref="B2:AG1199"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32596,7 +32596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6221AA-0D32-41F9-A1EC-7F9A3B86FEB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A805DF10-AB81-4DA5-8888-A92A940CB56E}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44998,7 +44998,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923DFD3A-1386-4CE4-B7C7-F283DAFB6830}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7A22E0-3D4C-45BB-86C9-7404A164AC34}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_AUS_grids_kan50/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E0E53-7B3D-48CF-99BA-EA039CCA0C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816973D2-2482-4700-BB00-D73C2C4213C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6205,7 +6205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD2C11B-2C48-4F2B-94D1-4E4EE040316A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53554EEB-0EA5-4A6D-B61C-C06F24F5AAD1}">
   <dimension ref="B2:AG1199"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32596,7 +32596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A805DF10-AB81-4DA5-8888-A92A940CB56E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4D2F75-9D28-46F9-BA1D-F0971DB93AF1}">
   <dimension ref="B9:L51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44998,7 +44998,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7A22E0-3D4C-45BB-86C9-7404A164AC34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC3C1E0-3F41-47EC-AF21-73229B0C5EC0}">
   <dimension ref="A1:I250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
